--- a/research/traditional_assets/database/data/serbia/serbia_machinery.xlsx
+++ b/research/traditional_assets/database/data/serbia/serbia_machinery.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1319558747206429</v>
+        <v>0.1317961909085619</v>
       </c>
       <c r="C2">
-        <v>24.62263715649025</v>
+        <v>24.38866919056957</v>
       </c>
       <c r="D2">
-        <v>13.72263715649025</v>
+        <v>13.73426919056957</v>
       </c>
       <c r="E2">
-        <v>-1.56</v>
+        <v>-1.3144</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2456</v>
       </c>
       <c r="G2">
         <v>10.9</v>
@@ -1451,28 +1451,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01235368</v>
       </c>
       <c r="N2">
-        <v>2.317959183673469</v>
+        <v>2.30560550367347</v>
       </c>
       <c r="O2">
-        <v>0.3476938775510204</v>
+        <v>0.3458408255510204</v>
       </c>
       <c r="P2">
-        <v>1.970265306122449</v>
+        <v>1.959764678122449</v>
       </c>
       <c r="Q2">
-        <v>3.050265306122449</v>
+        <v>3.039764678122449</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1319558747206429</v>
+        <v>0.1326955968773353</v>
       </c>
       <c r="T2">
-        <v>1.032125178898191</v>
+        <v>1.040986859727115</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>187.633092622884</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1317961909085619</v>
+        <v>0.1316365070964809</v>
       </c>
       <c r="C3">
-        <v>24.38866919056957</v>
+        <v>24.15472096123503</v>
       </c>
       <c r="D3">
-        <v>13.73426919056957</v>
+        <v>13.74592096123503</v>
       </c>
       <c r="E3">
-        <v>-1.3144</v>
+        <v>-1.0688</v>
       </c>
       <c r="F3">
-        <v>0.2456</v>
+        <v>0.4912</v>
       </c>
       <c r="G3">
         <v>10.9</v>
@@ -1533,28 +1533,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M3">
-        <v>0.01235368</v>
+        <v>0.02470736</v>
       </c>
       <c r="N3">
-        <v>2.30560550367347</v>
+        <v>2.29325182367347</v>
       </c>
       <c r="O3">
-        <v>0.3458408255510204</v>
+        <v>0.3439877735510204</v>
       </c>
       <c r="P3">
-        <v>1.959764678122449</v>
+        <v>1.949264050122449</v>
       </c>
       <c r="Q3">
-        <v>3.039764678122449</v>
+        <v>3.029264050122449</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1326955968773353</v>
+        <v>0.1334504154045724</v>
       </c>
       <c r="T3">
-        <v>1.040986859727115</v>
+        <v>1.050029391185201</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>187.633092622884</v>
+        <v>93.81654631144201</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1316365070964809</v>
+        <v>0.1314768232844</v>
       </c>
       <c r="C4">
-        <v>24.15472096123503</v>
+        <v>23.92079251876119</v>
       </c>
       <c r="D4">
-        <v>13.74592096123503</v>
+        <v>13.75759251876118</v>
       </c>
       <c r="E4">
-        <v>-1.0688</v>
+        <v>-0.8231999999999999</v>
       </c>
       <c r="F4">
-        <v>0.4912</v>
+        <v>0.7367999999999999</v>
       </c>
       <c r="G4">
         <v>10.9</v>
@@ -1615,28 +1615,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M4">
-        <v>0.02470736</v>
+        <v>0.03706104</v>
       </c>
       <c r="N4">
-        <v>2.29325182367347</v>
+        <v>2.280898143673469</v>
       </c>
       <c r="O4">
-        <v>0.3439877735510204</v>
+        <v>0.3421347215510204</v>
       </c>
       <c r="P4">
-        <v>1.949264050122449</v>
+        <v>1.938763422122449</v>
       </c>
       <c r="Q4">
-        <v>3.029264050122449</v>
+        <v>3.018763422122449</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1334504154045724</v>
+        <v>0.1342207972004124</v>
       </c>
       <c r="T4">
-        <v>1.050029391185201</v>
+        <v>1.059258366590875</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>93.81654631144201</v>
+        <v>62.54436420762799</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1314768232844</v>
+        <v>0.131317139472319</v>
       </c>
       <c r="C5">
-        <v>23.92079251876119</v>
+        <v>23.68688391359349</v>
       </c>
       <c r="D5">
-        <v>13.75759251876118</v>
+        <v>13.76928391359349</v>
       </c>
       <c r="E5">
-        <v>-0.8231999999999999</v>
+        <v>-0.5775999999999999</v>
       </c>
       <c r="F5">
-        <v>0.7367999999999999</v>
+        <v>0.9823999999999999</v>
       </c>
       <c r="G5">
         <v>10.9</v>
@@ -1697,28 +1697,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M5">
-        <v>0.03706104</v>
+        <v>0.04941472</v>
       </c>
       <c r="N5">
-        <v>2.280898143673469</v>
+        <v>2.268544463673469</v>
       </c>
       <c r="O5">
-        <v>0.3421347215510204</v>
+        <v>0.3402816695510204</v>
       </c>
       <c r="P5">
-        <v>1.938763422122449</v>
+        <v>1.928262794122449</v>
       </c>
       <c r="Q5">
-        <v>3.018763422122449</v>
+        <v>3.008262794122449</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1342207972004124</v>
+        <v>0.135007228616999</v>
       </c>
       <c r="T5">
-        <v>1.059258366590875</v>
+        <v>1.068679612317502</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>62.54436420762799</v>
+        <v>46.908273155721</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.131317139472319</v>
+        <v>0.1311574556602381</v>
       </c>
       <c r="C6">
-        <v>23.68688391359349</v>
+        <v>23.45299519634902</v>
       </c>
       <c r="D6">
-        <v>13.76928391359349</v>
+        <v>13.78099519634902</v>
       </c>
       <c r="E6">
-        <v>-0.5775999999999999</v>
+        <v>-0.3319999999999999</v>
       </c>
       <c r="F6">
-        <v>0.9823999999999999</v>
+        <v>1.228</v>
       </c>
       <c r="G6">
         <v>10.9</v>
@@ -1779,28 +1779,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M6">
-        <v>0.04941472</v>
+        <v>0.06176839999999999</v>
       </c>
       <c r="N6">
-        <v>2.268544463673469</v>
+        <v>2.256190783673469</v>
       </c>
       <c r="O6">
-        <v>0.3402816695510204</v>
+        <v>0.3384286175510204</v>
       </c>
       <c r="P6">
-        <v>1.928262794122449</v>
+        <v>1.917762166122449</v>
       </c>
       <c r="Q6">
-        <v>3.008262794122449</v>
+        <v>2.997762166122449</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.135007228616999</v>
+        <v>0.1358102164844611</v>
       </c>
       <c r="T6">
-        <v>1.068679612317502</v>
+        <v>1.078299200059426</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>46.908273155721</v>
+        <v>37.5266185245768</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1311574556602381</v>
+        <v>0.1309977718481571</v>
       </c>
       <c r="C7">
-        <v>23.45299519634902</v>
+        <v>23.21912641781721</v>
       </c>
       <c r="D7">
-        <v>13.78099519634902</v>
+        <v>13.79272641781722</v>
       </c>
       <c r="E7">
-        <v>-0.3319999999999999</v>
+        <v>-0.08639999999999981</v>
       </c>
       <c r="F7">
-        <v>1.228</v>
+        <v>1.4736</v>
       </c>
       <c r="G7">
         <v>10.9</v>
@@ -1861,28 +1861,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M7">
-        <v>0.06176839999999999</v>
+        <v>0.07412207999999999</v>
       </c>
       <c r="N7">
-        <v>2.256190783673469</v>
+        <v>2.243837103673469</v>
       </c>
       <c r="O7">
-        <v>0.3384286175510204</v>
+        <v>0.3365755655510204</v>
       </c>
       <c r="P7">
-        <v>1.917762166122449</v>
+        <v>1.907261538122449</v>
       </c>
       <c r="Q7">
-        <v>2.997762166122449</v>
+        <v>2.987261538122449</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1358102164844611</v>
+        <v>0.1366302892001671</v>
       </c>
       <c r="T7">
-        <v>1.078299200059426</v>
+        <v>1.088123459880965</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.5266185245768</v>
+        <v>31.272182103814</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1309977718481571</v>
+        <v>0.1308380880360761</v>
       </c>
       <c r="C8">
-        <v>23.21912641781721</v>
+        <v>22.98527762896058</v>
       </c>
       <c r="D8">
-        <v>13.79272641781722</v>
+        <v>13.80447762896058</v>
       </c>
       <c r="E8">
-        <v>-0.08640000000000003</v>
+        <v>0.1592</v>
       </c>
       <c r="F8">
-        <v>1.4736</v>
+        <v>1.7192</v>
       </c>
       <c r="G8">
         <v>10.9</v>
@@ -1943,28 +1943,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M8">
-        <v>0.07412207999999999</v>
+        <v>0.08647575999999998</v>
       </c>
       <c r="N8">
-        <v>2.243837103673469</v>
+        <v>2.23148342367347</v>
       </c>
       <c r="O8">
-        <v>0.3365755655510204</v>
+        <v>0.3347225135510204</v>
       </c>
       <c r="P8">
-        <v>1.907261538122449</v>
+        <v>1.896760910122449</v>
       </c>
       <c r="Q8">
-        <v>2.987261538122449</v>
+        <v>2.976760910122449</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1366302892001671</v>
+        <v>0.1374679978882539</v>
       </c>
       <c r="T8">
-        <v>1.088123459880965</v>
+        <v>1.098158994107269</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.272182103814</v>
+        <v>26.80472751755486</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1308380880360761</v>
+        <v>0.1306784042239952</v>
       </c>
       <c r="C9">
-        <v>22.98527762896058</v>
+        <v>22.75144888091547</v>
       </c>
       <c r="D9">
-        <v>13.80447762896058</v>
+        <v>13.81624888091547</v>
       </c>
       <c r="E9">
-        <v>0.1592000000000002</v>
+        <v>0.4048</v>
       </c>
       <c r="F9">
-        <v>1.7192</v>
+        <v>1.9648</v>
       </c>
       <c r="G9">
         <v>10.9</v>
@@ -2025,28 +2025,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M9">
-        <v>0.08647576</v>
+        <v>0.09882943999999999</v>
       </c>
       <c r="N9">
-        <v>2.23148342367347</v>
+        <v>2.21912974367347</v>
       </c>
       <c r="O9">
-        <v>0.3347225135510204</v>
+        <v>0.3328694615510204</v>
       </c>
       <c r="P9">
-        <v>1.896760910122449</v>
+        <v>1.886260282122449</v>
       </c>
       <c r="Q9">
-        <v>2.976760910122449</v>
+        <v>2.966260282122449</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1374679978882539</v>
+        <v>0.1383239176347773</v>
       </c>
       <c r="T9">
-        <v>1.098158994107269</v>
+        <v>1.108412692121101</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.80472751755486</v>
+        <v>23.4541365778605</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1306784042239952</v>
+        <v>0.1305187204119142</v>
       </c>
       <c r="C10">
-        <v>22.75144888091547</v>
+        <v>22.51764022499279</v>
       </c>
       <c r="D10">
-        <v>13.81624888091547</v>
+        <v>13.82804022499279</v>
       </c>
       <c r="E10">
-        <v>0.4048</v>
+        <v>0.6504000000000001</v>
       </c>
       <c r="F10">
-        <v>1.9648</v>
+        <v>2.2104</v>
       </c>
       <c r="G10">
         <v>10.9</v>
@@ -2107,28 +2107,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M10">
-        <v>0.09882943999999999</v>
+        <v>0.11118312</v>
       </c>
       <c r="N10">
-        <v>2.21912974367347</v>
+        <v>2.206776063673469</v>
       </c>
       <c r="O10">
-        <v>0.3328694615510204</v>
+        <v>0.3310164095510204</v>
       </c>
       <c r="P10">
-        <v>1.886260282122449</v>
+        <v>1.875759654122449</v>
       </c>
       <c r="Q10">
-        <v>2.966260282122449</v>
+        <v>2.955759654122449</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1383239176347773</v>
+        <v>0.1391986488043013</v>
       </c>
       <c r="T10">
-        <v>1.108412692121101</v>
+        <v>1.118891746135237</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.4541365778605</v>
+        <v>20.84812140254266</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1305187204119142</v>
+        <v>0.1303590365998333</v>
       </c>
       <c r="C11">
-        <v>22.51764022499279</v>
+        <v>22.28385171267876</v>
       </c>
       <c r="D11">
-        <v>13.82804022499279</v>
+        <v>13.83985171267876</v>
       </c>
       <c r="E11">
-        <v>0.6504000000000001</v>
+        <v>0.8959999999999997</v>
       </c>
       <c r="F11">
-        <v>2.2104</v>
+        <v>2.456</v>
       </c>
       <c r="G11">
         <v>10.9</v>
@@ -2189,28 +2189,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M11">
-        <v>0.11118312</v>
+        <v>0.1235368</v>
       </c>
       <c r="N11">
-        <v>2.206776063673469</v>
+        <v>2.194422383673469</v>
       </c>
       <c r="O11">
-        <v>0.3310164095510204</v>
+        <v>0.3291633575510204</v>
       </c>
       <c r="P11">
-        <v>1.875759654122449</v>
+        <v>1.865259026122449</v>
       </c>
       <c r="Q11">
-        <v>2.955759654122449</v>
+        <v>2.945259026122449</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1391986488043013</v>
+        <v>0.1400928184442592</v>
       </c>
       <c r="T11">
-        <v>1.118891746135237</v>
+        <v>1.129603668016354</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.84812140254266</v>
+        <v>18.7633092622884</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1303590365998333</v>
+        <v>0.1301993527877523</v>
       </c>
       <c r="C12">
-        <v>22.28385171267876</v>
+        <v>22.05008339563567</v>
       </c>
       <c r="D12">
-        <v>13.83985171267876</v>
+        <v>13.85168339563567</v>
       </c>
       <c r="E12">
-        <v>0.8960000000000001</v>
+        <v>1.1416</v>
       </c>
       <c r="F12">
-        <v>2.456</v>
+        <v>2.7016</v>
       </c>
       <c r="G12">
         <v>10.9</v>
@@ -2271,28 +2271,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M12">
-        <v>0.1235368</v>
+        <v>0.13589048</v>
       </c>
       <c r="N12">
-        <v>2.194422383673469</v>
+        <v>2.182068703673469</v>
       </c>
       <c r="O12">
-        <v>0.3291633575510204</v>
+        <v>0.3273103055510204</v>
       </c>
       <c r="P12">
-        <v>1.865259026122449</v>
+        <v>1.854758398122449</v>
       </c>
       <c r="Q12">
-        <v>2.945259026122449</v>
+        <v>2.934758398122449</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1400928184442592</v>
+        <v>0.1410070817839913</v>
       </c>
       <c r="T12">
-        <v>1.129603668016354</v>
+        <v>1.140556307243114</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.7633092622884</v>
+        <v>17.05755387480764</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1301993527877523</v>
+        <v>0.1300396689756713</v>
       </c>
       <c r="C13">
-        <v>22.05008339563567</v>
+        <v>21.81633532570263</v>
       </c>
       <c r="D13">
-        <v>13.85168339563567</v>
+        <v>13.86353532570262</v>
       </c>
       <c r="E13">
-        <v>1.1416</v>
+        <v>1.3872</v>
       </c>
       <c r="F13">
-        <v>2.7016</v>
+        <v>2.9472</v>
       </c>
       <c r="G13">
         <v>10.9</v>
@@ -2353,28 +2353,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M13">
-        <v>0.13589048</v>
+        <v>0.14824416</v>
       </c>
       <c r="N13">
-        <v>2.182068703673469</v>
+        <v>2.169715023673469</v>
       </c>
       <c r="O13">
-        <v>0.3273103055510204</v>
+        <v>0.3254572535510204</v>
       </c>
       <c r="P13">
-        <v>1.854758398122449</v>
+        <v>1.844257770122449</v>
       </c>
       <c r="Q13">
-        <v>2.934758398122449</v>
+        <v>2.924257770122449</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1410070817839913</v>
+        <v>0.1419421238359901</v>
       </c>
       <c r="T13">
-        <v>1.140556307243114</v>
+        <v>1.151757870088663</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.05755387480764</v>
+        <v>15.636091051907</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1300396689756713</v>
+        <v>0.1298799851635903</v>
       </c>
       <c r="C14">
-        <v>21.81633532570263</v>
+        <v>21.58260755489629</v>
       </c>
       <c r="D14">
-        <v>13.86353532570262</v>
+        <v>13.87540755489629</v>
       </c>
       <c r="E14">
-        <v>1.3872</v>
+        <v>1.6328</v>
       </c>
       <c r="F14">
-        <v>2.9472</v>
+        <v>3.1928</v>
       </c>
       <c r="G14">
         <v>10.9</v>
@@ -2435,28 +2435,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M14">
-        <v>0.14824416</v>
+        <v>0.16059784</v>
       </c>
       <c r="N14">
-        <v>2.169715023673469</v>
+        <v>2.15736134367347</v>
       </c>
       <c r="O14">
-        <v>0.3254572535510204</v>
+        <v>0.3236042015510204</v>
       </c>
       <c r="P14">
-        <v>1.844257770122449</v>
+        <v>1.833757142122449</v>
       </c>
       <c r="Q14">
-        <v>2.924257770122449</v>
+        <v>2.913757142122449</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1419421238359901</v>
+        <v>0.1428986611075751</v>
       </c>
       <c r="T14">
-        <v>1.151757870088663</v>
+        <v>1.163216940126065</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.636091051907</v>
+        <v>14.43331481714492</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1298799851635903</v>
+        <v>0.1297203013515094</v>
       </c>
       <c r="C15">
-        <v>21.58260755489629</v>
+        <v>21.34890013541168</v>
       </c>
       <c r="D15">
-        <v>13.87540755489629</v>
+        <v>13.88730013541168</v>
       </c>
       <c r="E15">
-        <v>1.6328</v>
+        <v>1.8784</v>
       </c>
       <c r="F15">
-        <v>3.1928</v>
+        <v>3.4384</v>
       </c>
       <c r="G15">
         <v>10.9</v>
@@ -2517,28 +2517,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M15">
-        <v>0.16059784</v>
+        <v>0.17295152</v>
       </c>
       <c r="N15">
-        <v>2.15736134367347</v>
+        <v>2.14500766367347</v>
       </c>
       <c r="O15">
-        <v>0.3236042015510204</v>
+        <v>0.3217511495510204</v>
       </c>
       <c r="P15">
-        <v>1.833757142122449</v>
+        <v>1.823256514122449</v>
       </c>
       <c r="Q15">
-        <v>2.913757142122449</v>
+        <v>2.903256514122449</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1428986611075751</v>
+        <v>0.1438774434319876</v>
       </c>
       <c r="T15">
-        <v>1.163216940126065</v>
+        <v>1.174942500164336</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.43331481714492</v>
+        <v>13.40236375877743</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1297203013515094</v>
+        <v>0.1297518675394284</v>
       </c>
       <c r="C16">
-        <v>21.34890013541168</v>
+        <v>21.10094760176781</v>
       </c>
       <c r="D16">
-        <v>13.88730013541168</v>
+        <v>13.88494760176781</v>
       </c>
       <c r="E16">
-        <v>1.8784</v>
+        <v>2.124000000000001</v>
       </c>
       <c r="F16">
-        <v>3.4384</v>
+        <v>3.684</v>
       </c>
       <c r="G16">
         <v>10.9</v>
@@ -2599,45 +2599,45 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M16">
-        <v>0.17295152</v>
+        <v>0.1908312</v>
       </c>
       <c r="N16">
-        <v>2.14500766367347</v>
+        <v>2.12712798367347</v>
       </c>
       <c r="O16">
-        <v>0.3217511495510204</v>
+        <v>0.3190691975510204</v>
       </c>
       <c r="P16">
-        <v>1.823256514122449</v>
+        <v>1.808058786122449</v>
       </c>
       <c r="Q16">
-        <v>2.903256514122449</v>
+        <v>2.888058786122449</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1438774434319876</v>
+        <v>0.1448792559287393</v>
       </c>
       <c r="T16">
-        <v>1.174942500164336</v>
+        <v>1.18694395573292</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.15</v>
       </c>
       <c r="W16">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.40236375877743</v>
+        <v>12.14664679399107</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1297518675394284</v>
+        <v>0.1296049337273474</v>
       </c>
       <c r="C17">
-        <v>21.10094760176781</v>
+        <v>20.86630492476704</v>
       </c>
       <c r="D17">
-        <v>13.88494760176781</v>
+        <v>13.89590492476704</v>
       </c>
       <c r="E17">
-        <v>2.124</v>
+        <v>2.3696</v>
       </c>
       <c r="F17">
-        <v>3.684</v>
+        <v>3.9296</v>
       </c>
       <c r="G17">
         <v>10.9</v>
@@ -2681,28 +2681,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M17">
-        <v>0.1908312</v>
+        <v>0.20355328</v>
       </c>
       <c r="N17">
-        <v>2.12712798367347</v>
+        <v>2.114405903673469</v>
       </c>
       <c r="O17">
-        <v>0.3190691975510204</v>
+        <v>0.3171608855510204</v>
       </c>
       <c r="P17">
-        <v>1.808058786122449</v>
+        <v>1.797245018122449</v>
       </c>
       <c r="Q17">
-        <v>2.888058786122449</v>
+        <v>2.877245018122449</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1448792559287393</v>
+        <v>0.1459049211039851</v>
       </c>
       <c r="T17">
-        <v>1.18694395573292</v>
+        <v>1.199231160243613</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.14664679399108</v>
+        <v>11.38748136936663</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1296049337273474</v>
+        <v>0.1294579999152665</v>
       </c>
       <c r="C18">
-        <v>20.86630492476704</v>
+        <v>20.6316795553937</v>
       </c>
       <c r="D18">
-        <v>13.89590492476704</v>
+        <v>13.9068795553937</v>
       </c>
       <c r="E18">
-        <v>2.3696</v>
+        <v>2.615200000000001</v>
       </c>
       <c r="F18">
-        <v>3.9296</v>
+        <v>4.1752</v>
       </c>
       <c r="G18">
         <v>10.9</v>
@@ -2763,28 +2763,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M18">
-        <v>0.20355328</v>
+        <v>0.21627536</v>
       </c>
       <c r="N18">
-        <v>2.114405903673469</v>
+        <v>2.101683823673469</v>
       </c>
       <c r="O18">
-        <v>0.3171608855510204</v>
+        <v>0.3152525735510204</v>
       </c>
       <c r="P18">
-        <v>1.797245018122449</v>
+        <v>1.786431250122449</v>
       </c>
       <c r="Q18">
-        <v>2.877245018122449</v>
+        <v>2.866431250122449</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1459049211039851</v>
+        <v>0.1469553011027307</v>
       </c>
       <c r="T18">
-        <v>1.199231160243613</v>
+        <v>1.21181444197143</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.38748136936663</v>
+        <v>10.71762952410977</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1294579999152665</v>
+        <v>0.1293110661031855</v>
       </c>
       <c r="C19">
-        <v>20.6316795553937</v>
+        <v>20.39707153468755</v>
       </c>
       <c r="D19">
-        <v>13.9068795553937</v>
+        <v>13.91787153468755</v>
       </c>
       <c r="E19">
-        <v>2.615200000000001</v>
+        <v>2.860800000000001</v>
       </c>
       <c r="F19">
-        <v>4.1752</v>
+        <v>4.420800000000001</v>
       </c>
       <c r="G19">
         <v>10.9</v>
@@ -2845,28 +2845,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M19">
-        <v>0.21627536</v>
+        <v>0.22899744</v>
       </c>
       <c r="N19">
-        <v>2.101683823673469</v>
+        <v>2.088961743673469</v>
       </c>
       <c r="O19">
-        <v>0.3152525735510204</v>
+        <v>0.3133442615510204</v>
       </c>
       <c r="P19">
-        <v>1.786431250122449</v>
+        <v>1.775617482122449</v>
       </c>
       <c r="Q19">
-        <v>2.866431250122449</v>
+        <v>2.855617482122449</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1469553011027307</v>
+        <v>0.148031300125836</v>
       </c>
       <c r="T19">
-        <v>1.21181444197143</v>
+        <v>1.224704633009683</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.71762952410977</v>
+        <v>10.12220566165923</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1293110661031855</v>
+        <v>0.1294386822911046</v>
       </c>
       <c r="C20">
-        <v>20.39707153468754</v>
+        <v>20.1419236971782</v>
       </c>
       <c r="D20">
-        <v>13.91787153468754</v>
+        <v>13.90832369717819</v>
       </c>
       <c r="E20">
-        <v>2.8608</v>
+        <v>3.1064</v>
       </c>
       <c r="F20">
-        <v>4.4208</v>
+        <v>4.666399999999999</v>
       </c>
       <c r="G20">
         <v>10.9</v>
@@ -2927,45 +2927,45 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M20">
-        <v>0.22899744</v>
+        <v>0.2496524</v>
       </c>
       <c r="N20">
-        <v>2.088961743673469</v>
+        <v>2.068306783673469</v>
       </c>
       <c r="O20">
-        <v>0.3133442615510204</v>
+        <v>0.3102460175510204</v>
       </c>
       <c r="P20">
-        <v>1.775617482122449</v>
+        <v>1.758060766122449</v>
       </c>
       <c r="Q20">
-        <v>2.855617482122449</v>
+        <v>2.838060766122449</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.148031300125836</v>
+        <v>0.149133867026055</v>
       </c>
       <c r="T20">
-        <v>1.224704633009683</v>
+        <v>1.237913100369867</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.15</v>
       </c>
       <c r="W20">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.12220566165923</v>
+        <v>9.284746245874143</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1294386822911046</v>
+        <v>0.1293061984790236</v>
       </c>
       <c r="C21">
-        <v>20.1419236971782</v>
+        <v>19.90623597440033</v>
       </c>
       <c r="D21">
-        <v>13.90832369717819</v>
+        <v>13.91823597440033</v>
       </c>
       <c r="E21">
-        <v>3.1064</v>
+        <v>3.352</v>
       </c>
       <c r="F21">
-        <v>4.666399999999999</v>
+        <v>4.912</v>
       </c>
       <c r="G21">
         <v>10.9</v>
@@ -3009,28 +3009,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M21">
-        <v>0.2496524</v>
+        <v>0.262792</v>
       </c>
       <c r="N21">
-        <v>2.068306783673469</v>
+        <v>2.055167183673469</v>
       </c>
       <c r="O21">
-        <v>0.3102460175510204</v>
+        <v>0.3082750775510204</v>
       </c>
       <c r="P21">
-        <v>1.758060766122449</v>
+        <v>1.746892106122449</v>
       </c>
       <c r="Q21">
-        <v>2.838060766122449</v>
+        <v>2.826892106122449</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.149133867026055</v>
+        <v>0.1502639980987795</v>
       </c>
       <c r="T21">
-        <v>1.237913100369867</v>
+        <v>1.251451779414057</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.284746245874143</v>
+        <v>8.820508933580435</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1293061984790236</v>
+        <v>0.1291737146669426</v>
       </c>
       <c r="C22">
-        <v>19.90623597440033</v>
+        <v>19.67056239039513</v>
       </c>
       <c r="D22">
-        <v>13.91823597440033</v>
+        <v>13.92816239039513</v>
       </c>
       <c r="E22">
-        <v>3.352</v>
+        <v>3.597600000000001</v>
       </c>
       <c r="F22">
-        <v>4.912</v>
+        <v>5.1576</v>
       </c>
       <c r="G22">
         <v>10.9</v>
@@ -3091,28 +3091,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M22">
-        <v>0.262792</v>
+        <v>0.2759316</v>
       </c>
       <c r="N22">
-        <v>2.055167183673469</v>
+        <v>2.04202758367347</v>
       </c>
       <c r="O22">
-        <v>0.3082750775510204</v>
+        <v>0.3063041375510204</v>
       </c>
       <c r="P22">
-        <v>1.746892106122449</v>
+        <v>1.735723446122449</v>
       </c>
       <c r="Q22">
-        <v>2.826892106122449</v>
+        <v>2.815723446122449</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1502639980987795</v>
+        <v>0.1514227400847375</v>
       </c>
       <c r="T22">
-        <v>1.251451779414057</v>
+        <v>1.265333209826453</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.820508933580435</v>
+        <v>8.400484698648032</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1291737146669426</v>
+        <v>0.1290412308548617</v>
       </c>
       <c r="C23">
-        <v>19.67056239039513</v>
+        <v>19.43490297543529</v>
       </c>
       <c r="D23">
-        <v>13.92816239039513</v>
+        <v>13.93810297543529</v>
       </c>
       <c r="E23">
-        <v>3.5976</v>
+        <v>3.8432</v>
       </c>
       <c r="F23">
-        <v>5.1576</v>
+        <v>5.4032</v>
       </c>
       <c r="G23">
         <v>10.9</v>
@@ -3173,28 +3173,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M23">
-        <v>0.2759315999999999</v>
+        <v>0.2890712</v>
       </c>
       <c r="N23">
-        <v>2.04202758367347</v>
+        <v>2.028887983673469</v>
       </c>
       <c r="O23">
-        <v>0.3063041375510204</v>
+        <v>0.3043331975510204</v>
       </c>
       <c r="P23">
-        <v>1.735723446122449</v>
+        <v>1.724554786122449</v>
       </c>
       <c r="Q23">
-        <v>2.815723446122449</v>
+        <v>2.804554786122449</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1514227400847375</v>
+        <v>0.1526111934036688</v>
       </c>
       <c r="T23">
-        <v>1.265333209826453</v>
+        <v>1.279570574351988</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.400484698648034</v>
+        <v>8.018644485073121</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1290412308548617</v>
+        <v>0.1289087470427807</v>
       </c>
       <c r="C24">
-        <v>19.43490297543529</v>
+        <v>19.19925775987999</v>
       </c>
       <c r="D24">
-        <v>13.93810297543529</v>
+        <v>13.94805775987999</v>
       </c>
       <c r="E24">
-        <v>3.8432</v>
+        <v>4.0888</v>
       </c>
       <c r="F24">
-        <v>5.4032</v>
+        <v>5.6488</v>
       </c>
       <c r="G24">
         <v>10.9</v>
@@ -3255,28 +3255,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M24">
-        <v>0.2890712</v>
+        <v>0.3022107999999999</v>
       </c>
       <c r="N24">
-        <v>2.028887983673469</v>
+        <v>2.015748383673469</v>
       </c>
       <c r="O24">
-        <v>0.3043331975510204</v>
+        <v>0.3023622575510204</v>
       </c>
       <c r="P24">
-        <v>1.724554786122449</v>
+        <v>1.713386126122449</v>
       </c>
       <c r="Q24">
-        <v>2.804554786122449</v>
+        <v>2.793386126122449</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1526111934036688</v>
+        <v>0.1538305156399749</v>
       </c>
       <c r="T24">
-        <v>1.279570574351988</v>
+        <v>1.294177740553511</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.018644485073121</v>
+        <v>7.670007768330813</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1289087470427807</v>
+        <v>0.1289394632306997</v>
       </c>
       <c r="C25">
-        <v>19.19925775987999</v>
+        <v>18.95134849090878</v>
       </c>
       <c r="D25">
-        <v>13.94805775987999</v>
+        <v>13.94574849090878</v>
       </c>
       <c r="E25">
-        <v>4.0888</v>
+        <v>4.3344</v>
       </c>
       <c r="F25">
-        <v>5.6488</v>
+        <v>5.8944</v>
       </c>
       <c r="G25">
         <v>10.9</v>
@@ -3337,45 +3337,45 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M25">
-        <v>0.3022107999999999</v>
+        <v>0.32006592</v>
       </c>
       <c r="N25">
-        <v>2.015748383673469</v>
+        <v>1.997893263673469</v>
       </c>
       <c r="O25">
-        <v>0.3023622575510204</v>
+        <v>0.2996839895510204</v>
       </c>
       <c r="P25">
-        <v>1.713386126122449</v>
+        <v>1.698209274122449</v>
       </c>
       <c r="Q25">
-        <v>2.793386126122449</v>
+        <v>2.778209274122449</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1538305156399749</v>
+        <v>0.1550819253035523</v>
       </c>
       <c r="T25">
-        <v>1.294177740553511</v>
+        <v>1.3091693058656</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.15</v>
       </c>
       <c r="W25">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.670007768330813</v>
+        <v>7.242130570082155</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1289394632306997</v>
+        <v>0.1288137794186188</v>
       </c>
       <c r="C26">
-        <v>18.95134849090878</v>
+        <v>18.7152023461883</v>
       </c>
       <c r="D26">
-        <v>13.94574849090878</v>
+        <v>13.9552023461883</v>
       </c>
       <c r="E26">
-        <v>4.3344</v>
+        <v>4.58</v>
       </c>
       <c r="F26">
-        <v>5.894399999999999</v>
+        <v>6.14</v>
       </c>
       <c r="G26">
         <v>10.9</v>
@@ -3419,28 +3419,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M26">
-        <v>0.3200659199999999</v>
+        <v>0.333402</v>
       </c>
       <c r="N26">
-        <v>1.997893263673469</v>
+        <v>1.984557183673469</v>
       </c>
       <c r="O26">
-        <v>0.2996839895510204</v>
+        <v>0.2976835775510204</v>
       </c>
       <c r="P26">
-        <v>1.698209274122449</v>
+        <v>1.686873606122449</v>
       </c>
       <c r="Q26">
-        <v>2.778209274122449</v>
+        <v>2.766873606122449</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1550819253035523</v>
+        <v>0.1563667058914917</v>
       </c>
       <c r="T26">
-        <v>1.3091693058656</v>
+        <v>1.324560646252678</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.242130570082156</v>
+        <v>6.95244534727887</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1288137794186188</v>
+        <v>0.1286880956065378</v>
       </c>
       <c r="C27">
-        <v>18.7152023461883</v>
+        <v>18.47906902774366</v>
       </c>
       <c r="D27">
-        <v>13.9552023461883</v>
+        <v>13.96466902774366</v>
       </c>
       <c r="E27">
-        <v>4.58</v>
+        <v>4.825600000000001</v>
       </c>
       <c r="F27">
-        <v>6.14</v>
+        <v>6.3856</v>
       </c>
       <c r="G27">
         <v>10.9</v>
@@ -3501,28 +3501,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M27">
-        <v>0.333402</v>
+        <v>0.34673808</v>
       </c>
       <c r="N27">
-        <v>1.984557183673469</v>
+        <v>1.971221103673469</v>
       </c>
       <c r="O27">
-        <v>0.2976835775510204</v>
+        <v>0.2956831655510204</v>
       </c>
       <c r="P27">
-        <v>1.686873606122449</v>
+        <v>1.675537938122449</v>
       </c>
       <c r="Q27">
-        <v>2.766873606122449</v>
+        <v>2.755537938122449</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1563667058914917</v>
+        <v>0.1576862102791051</v>
       </c>
       <c r="T27">
-        <v>1.324560646252678</v>
+        <v>1.340367968812381</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.95244534727887</v>
+        <v>6.685043603152758</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1286880956065378</v>
+        <v>0.1285624117944568</v>
       </c>
       <c r="C28">
-        <v>18.47906902774366</v>
+        <v>18.24294856169517</v>
       </c>
       <c r="D28">
-        <v>13.96466902774366</v>
+        <v>13.97414856169517</v>
       </c>
       <c r="E28">
-        <v>4.825600000000001</v>
+        <v>5.0712</v>
       </c>
       <c r="F28">
-        <v>6.3856</v>
+        <v>6.6312</v>
       </c>
       <c r="G28">
         <v>10.9</v>
@@ -3583,28 +3583,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M28">
-        <v>0.34673808</v>
+        <v>0.36007416</v>
       </c>
       <c r="N28">
-        <v>1.971221103673469</v>
+        <v>1.95788502367347</v>
       </c>
       <c r="O28">
-        <v>0.2956831655510204</v>
+        <v>0.2936827535510204</v>
       </c>
       <c r="P28">
-        <v>1.675537938122449</v>
+        <v>1.664202270122449</v>
       </c>
       <c r="Q28">
-        <v>2.755537938122449</v>
+        <v>2.744202270122449</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1576862102791051</v>
+        <v>0.1590418654718587</v>
       </c>
       <c r="T28">
-        <v>1.340367968812381</v>
+        <v>1.356608368702485</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.685043603152758</v>
+        <v>6.437449395628583</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1285624117944568</v>
+        <v>0.1284367279823759</v>
       </c>
       <c r="C29">
-        <v>18.24294856169517</v>
+        <v>18.00684097423411</v>
       </c>
       <c r="D29">
-        <v>13.97414856169517</v>
+        <v>13.98364097423411</v>
       </c>
       <c r="E29">
-        <v>5.0712</v>
+        <v>5.316800000000001</v>
       </c>
       <c r="F29">
-        <v>6.6312</v>
+        <v>6.8768</v>
       </c>
       <c r="G29">
         <v>10.9</v>
@@ -3665,28 +3665,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M29">
-        <v>0.36007416</v>
+        <v>0.37341024</v>
       </c>
       <c r="N29">
-        <v>1.95788502367347</v>
+        <v>1.944548943673469</v>
       </c>
       <c r="O29">
-        <v>0.2936827535510204</v>
+        <v>0.2916823415510204</v>
       </c>
       <c r="P29">
-        <v>1.664202270122449</v>
+        <v>1.652866602122449</v>
       </c>
       <c r="Q29">
-        <v>2.744202270122449</v>
+        <v>2.732866602122449</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1590418654718587</v>
+        <v>0.1604351777532998</v>
       </c>
       <c r="T29">
-        <v>1.356608368702485</v>
+        <v>1.37329989081176</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.437449395628583</v>
+        <v>6.207540488641847</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1284367279823759</v>
+        <v>0.1285575441702949</v>
       </c>
       <c r="C30">
-        <v>18.00684097423411</v>
+        <v>17.75211595463533</v>
       </c>
       <c r="D30">
-        <v>13.98364097423411</v>
+        <v>13.97451595463533</v>
       </c>
       <c r="E30">
-        <v>5.316800000000001</v>
+        <v>5.562400000000001</v>
       </c>
       <c r="F30">
-        <v>6.8768</v>
+        <v>7.122400000000001</v>
       </c>
       <c r="G30">
         <v>10.9</v>
@@ -3747,45 +3747,45 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M30">
-        <v>0.37341024</v>
+        <v>0.3938687200000001</v>
       </c>
       <c r="N30">
-        <v>1.944548943673469</v>
+        <v>1.924090463673469</v>
       </c>
       <c r="O30">
-        <v>0.2916823415510204</v>
+        <v>0.2886135695510204</v>
       </c>
       <c r="P30">
-        <v>1.652866602122449</v>
+        <v>1.635476894122449</v>
       </c>
       <c r="Q30">
-        <v>2.732866602122449</v>
+        <v>2.715476894122449</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1604351777532998</v>
+        <v>0.161867738268021</v>
       </c>
       <c r="T30">
-        <v>1.37329989081176</v>
+        <v>1.390461596642422</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.15</v>
       </c>
       <c r="W30">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.207540488641847</v>
+        <v>5.88510604161069</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1285575441702949</v>
+        <v>0.1284403603582139</v>
       </c>
       <c r="C31">
-        <v>17.75211595463533</v>
+        <v>17.51536645396188</v>
       </c>
       <c r="D31">
-        <v>13.97451595463533</v>
+        <v>13.98336645396188</v>
       </c>
       <c r="E31">
-        <v>5.562399999999999</v>
+        <v>5.808</v>
       </c>
       <c r="F31">
-        <v>7.122399999999999</v>
+        <v>7.367999999999999</v>
       </c>
       <c r="G31">
         <v>10.9</v>
@@ -3829,28 +3829,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M31">
-        <v>0.3938687199999999</v>
+        <v>0.4074504</v>
       </c>
       <c r="N31">
-        <v>1.924090463673469</v>
+        <v>1.910508783673469</v>
       </c>
       <c r="O31">
-        <v>0.2886135695510204</v>
+        <v>0.2865763175510204</v>
       </c>
       <c r="P31">
-        <v>1.635476894122449</v>
+        <v>1.623932466122449</v>
       </c>
       <c r="Q31">
-        <v>2.715476894122449</v>
+        <v>2.703932466122449</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.161867738268021</v>
+        <v>0.1633412290831628</v>
       </c>
       <c r="T31">
-        <v>1.390461596642422</v>
+        <v>1.408113636925389</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.885106041610691</v>
+        <v>5.688935840223667</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1284403603582139</v>
+        <v>0.128323176546133</v>
       </c>
       <c r="C32">
-        <v>17.51536645396188</v>
+        <v>17.27862817099066</v>
       </c>
       <c r="D32">
-        <v>13.98336645396188</v>
+        <v>13.99222817099066</v>
       </c>
       <c r="E32">
-        <v>5.808</v>
+        <v>6.0536</v>
       </c>
       <c r="F32">
-        <v>7.367999999999999</v>
+        <v>7.6136</v>
       </c>
       <c r="G32">
         <v>10.9</v>
@@ -3911,28 +3911,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M32">
-        <v>0.4074504</v>
+        <v>0.42103208</v>
       </c>
       <c r="N32">
-        <v>1.910508783673469</v>
+        <v>1.896927103673469</v>
       </c>
       <c r="O32">
-        <v>0.2865763175510204</v>
+        <v>0.2845390655510204</v>
       </c>
       <c r="P32">
-        <v>1.623932466122449</v>
+        <v>1.612388038122449</v>
       </c>
       <c r="Q32">
-        <v>2.703932466122449</v>
+        <v>2.692388038122449</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1633412290831628</v>
+        <v>0.1648574297770043</v>
       </c>
       <c r="T32">
-        <v>1.408113636925389</v>
+        <v>1.426277330549892</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.688935840223667</v>
+        <v>5.505421780861614</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.128323176546133</v>
+        <v>0.128205992734052</v>
       </c>
       <c r="C33">
-        <v>17.27862817099066</v>
+        <v>17.04190112706228</v>
       </c>
       <c r="D33">
-        <v>13.99222817099066</v>
+        <v>14.00110112706228</v>
       </c>
       <c r="E33">
-        <v>6.0536</v>
+        <v>6.2992</v>
       </c>
       <c r="F33">
-        <v>7.6136</v>
+        <v>7.8592</v>
       </c>
       <c r="G33">
         <v>10.9</v>
@@ -3993,28 +3993,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M33">
-        <v>0.42103208</v>
+        <v>0.43461376</v>
       </c>
       <c r="N33">
-        <v>1.896927103673469</v>
+        <v>1.883345423673469</v>
       </c>
       <c r="O33">
-        <v>0.2845390655510204</v>
+        <v>0.2825018135510204</v>
       </c>
       <c r="P33">
-        <v>1.612388038122449</v>
+        <v>1.600843610122449</v>
       </c>
       <c r="Q33">
-        <v>2.692388038122449</v>
+        <v>2.680843610122449</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1648574297770043</v>
+        <v>0.1664182246089</v>
       </c>
       <c r="T33">
-        <v>1.426277330549892</v>
+        <v>1.444975250457468</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.505421780861614</v>
+        <v>5.333377350209688</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.128205992734052</v>
+        <v>0.1280888089219711</v>
       </c>
       <c r="C34">
-        <v>17.04190112706228</v>
+        <v>16.80518534357151</v>
       </c>
       <c r="D34">
-        <v>14.00110112706228</v>
+        <v>14.00998534357151</v>
       </c>
       <c r="E34">
-        <v>6.2992</v>
+        <v>6.5448</v>
       </c>
       <c r="F34">
-        <v>7.8592</v>
+        <v>8.104799999999999</v>
       </c>
       <c r="G34">
         <v>10.9</v>
@@ -4075,28 +4075,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M34">
-        <v>0.43461376</v>
+        <v>0.4481954399999999</v>
       </c>
       <c r="N34">
-        <v>1.883345423673469</v>
+        <v>1.86976374367347</v>
       </c>
       <c r="O34">
-        <v>0.2825018135510204</v>
+        <v>0.2804645615510204</v>
       </c>
       <c r="P34">
-        <v>1.600843610122449</v>
+        <v>1.589299182122449</v>
       </c>
       <c r="Q34">
-        <v>2.680843610122449</v>
+        <v>2.669299182122449</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1664182246089</v>
+        <v>0.1680256103313001</v>
       </c>
       <c r="T34">
-        <v>1.444975250457468</v>
+        <v>1.464231317227956</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.333377350209688</v>
+        <v>5.17175985474879</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1280888089219711</v>
+        <v>0.1279716251098901</v>
       </c>
       <c r="C35">
-        <v>16.80518534357151</v>
+        <v>16.56848084196745</v>
       </c>
       <c r="D35">
-        <v>14.00998534357151</v>
+        <v>14.01888084196745</v>
       </c>
       <c r="E35">
-        <v>6.5448</v>
+        <v>6.790400000000001</v>
       </c>
       <c r="F35">
-        <v>8.104799999999999</v>
+        <v>8.3504</v>
       </c>
       <c r="G35">
         <v>10.9</v>
@@ -4157,28 +4157,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M35">
-        <v>0.4481954399999999</v>
+        <v>0.46177712</v>
       </c>
       <c r="N35">
-        <v>1.86976374367347</v>
+        <v>1.856182063673469</v>
       </c>
       <c r="O35">
-        <v>0.2804645615510204</v>
+        <v>0.2784273095510204</v>
       </c>
       <c r="P35">
-        <v>1.589299182122449</v>
+        <v>1.577754754122449</v>
       </c>
       <c r="Q35">
-        <v>2.669299182122449</v>
+        <v>2.657754754122449</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1680256103313001</v>
+        <v>0.1696817047119547</v>
       </c>
       <c r="T35">
-        <v>1.464231317227956</v>
+        <v>1.484070901173308</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.17175985474879</v>
+        <v>5.019649270785589</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1279716251098901</v>
+        <v>0.1278544412978091</v>
       </c>
       <c r="C36">
-        <v>16.56848084196745</v>
+        <v>16.3317876437537</v>
       </c>
       <c r="D36">
-        <v>14.01888084196745</v>
+        <v>14.0277876437537</v>
       </c>
       <c r="E36">
-        <v>6.790400000000001</v>
+        <v>7.036</v>
       </c>
       <c r="F36">
-        <v>8.3504</v>
+        <v>8.596</v>
       </c>
       <c r="G36">
         <v>10.9</v>
@@ -4239,28 +4239,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M36">
-        <v>0.46177712</v>
+        <v>0.4753588</v>
       </c>
       <c r="N36">
-        <v>1.856182063673469</v>
+        <v>1.842600383673469</v>
       </c>
       <c r="O36">
-        <v>0.2784273095510204</v>
+        <v>0.2763900575510204</v>
       </c>
       <c r="P36">
-        <v>1.577754754122449</v>
+        <v>1.566210326122449</v>
       </c>
       <c r="Q36">
-        <v>2.657754754122449</v>
+        <v>2.646210326122449</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1696817047119547</v>
+        <v>0.1713887558427833</v>
       </c>
       <c r="T36">
-        <v>1.484070901173308</v>
+        <v>1.50452093385544</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.019649270785589</v>
+        <v>4.876230720191715</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1278544412978091</v>
+        <v>0.1277372574857281</v>
       </c>
       <c r="C37">
-        <v>16.3317876437537</v>
+        <v>16.09510577048857</v>
       </c>
       <c r="D37">
-        <v>14.0277876437537</v>
+        <v>14.03670577048857</v>
       </c>
       <c r="E37">
-        <v>7.036</v>
+        <v>7.281600000000002</v>
       </c>
       <c r="F37">
-        <v>8.596</v>
+        <v>8.841600000000001</v>
       </c>
       <c r="G37">
         <v>10.9</v>
@@ -4321,28 +4321,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M37">
-        <v>0.4753588</v>
+        <v>0.4889404800000001</v>
       </c>
       <c r="N37">
-        <v>1.842600383673469</v>
+        <v>1.829018703673469</v>
       </c>
       <c r="O37">
-        <v>0.2763900575510204</v>
+        <v>0.2743528055510204</v>
       </c>
       <c r="P37">
-        <v>1.566210326122449</v>
+        <v>1.554665898122449</v>
       </c>
       <c r="Q37">
-        <v>2.646210326122449</v>
+        <v>2.634665898122449</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1713887558427833</v>
+        <v>0.1731491523214503</v>
       </c>
       <c r="T37">
-        <v>1.50452093385544</v>
+        <v>1.525610030058889</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.876230720191715</v>
+        <v>4.740779866853055</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1277372574857282</v>
+        <v>0.1276200736736472</v>
       </c>
       <c r="C38">
-        <v>16.09510577048857</v>
+        <v>15.85843524378522</v>
       </c>
       <c r="D38">
-        <v>14.03670577048857</v>
+        <v>14.04563524378521</v>
       </c>
       <c r="E38">
-        <v>7.2816</v>
+        <v>7.5272</v>
       </c>
       <c r="F38">
-        <v>8.8416</v>
+        <v>9.087199999999999</v>
       </c>
       <c r="G38">
         <v>10.9</v>
@@ -4403,28 +4403,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M38">
-        <v>0.48894048</v>
+        <v>0.5025221599999999</v>
       </c>
       <c r="N38">
-        <v>1.829018703673469</v>
+        <v>1.81543702367347</v>
       </c>
       <c r="O38">
-        <v>0.2743528055510204</v>
+        <v>0.2723155535510204</v>
       </c>
       <c r="P38">
-        <v>1.554665898122449</v>
+        <v>1.543121470122449</v>
       </c>
       <c r="Q38">
-        <v>2.634665898122449</v>
+        <v>2.623121470122449</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1731491523214503</v>
+        <v>0.1749654344026146</v>
       </c>
       <c r="T38">
-        <v>1.525610030058889</v>
+        <v>1.547368621379907</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.740779866853056</v>
+        <v>4.612650681262433</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1276200736736472</v>
+        <v>0.1283103898615662</v>
       </c>
       <c r="C39">
-        <v>15.85843524378522</v>
+        <v>15.56039581002691</v>
       </c>
       <c r="D39">
-        <v>14.04563524378521</v>
+        <v>13.99319581002691</v>
       </c>
       <c r="E39">
-        <v>7.5272</v>
+        <v>7.772799999999999</v>
       </c>
       <c r="F39">
-        <v>9.087199999999999</v>
+        <v>9.332799999999999</v>
       </c>
       <c r="G39">
         <v>10.9</v>
@@ -4485,45 +4485,45 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M39">
-        <v>0.5025221599999999</v>
+        <v>0.53943584</v>
       </c>
       <c r="N39">
-        <v>1.81543702367347</v>
+        <v>1.77852334367347</v>
       </c>
       <c r="O39">
-        <v>0.2723155535510204</v>
+        <v>0.2667785015510204</v>
       </c>
       <c r="P39">
-        <v>1.543121470122449</v>
+        <v>1.511744842122449</v>
       </c>
       <c r="Q39">
-        <v>2.623121470122449</v>
+        <v>2.591744842122449</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1749654344026146</v>
+        <v>0.1768403062283326</v>
       </c>
       <c r="T39">
-        <v>1.547368621379907</v>
+        <v>1.569829102743539</v>
       </c>
       <c r="U39">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.15</v>
       </c>
       <c r="W39">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.612650681262433</v>
+        <v>4.297006264310264</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1283103898615662</v>
+        <v>0.1282144560494853</v>
       </c>
       <c r="C40">
-        <v>15.56039581002691</v>
+        <v>15.32205992241501</v>
       </c>
       <c r="D40">
-        <v>13.99319581002691</v>
+        <v>14.00045992241501</v>
       </c>
       <c r="E40">
-        <v>7.772799999999999</v>
+        <v>8.0184</v>
       </c>
       <c r="F40">
-        <v>9.332799999999999</v>
+        <v>9.5784</v>
       </c>
       <c r="G40">
         <v>10.9</v>
@@ -4567,28 +4567,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M40">
-        <v>0.53943584</v>
+        <v>0.55363152</v>
       </c>
       <c r="N40">
-        <v>1.77852334367347</v>
+        <v>1.764327663673469</v>
       </c>
       <c r="O40">
-        <v>0.2667785015510204</v>
+        <v>0.2646491495510204</v>
       </c>
       <c r="P40">
-        <v>1.511744842122449</v>
+        <v>1.499678514122449</v>
       </c>
       <c r="Q40">
-        <v>2.591744842122449</v>
+        <v>2.579678514122449</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1768403062283326</v>
+        <v>0.1787766492614513</v>
       </c>
       <c r="T40">
-        <v>1.569829102743539</v>
+        <v>1.593025993332208</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.297006264310264</v>
+        <v>4.186826616507437</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1282144560494853</v>
+        <v>0.1281185222374043</v>
       </c>
       <c r="C41">
-        <v>15.32205992241501</v>
+        <v>15.08373158057552</v>
       </c>
       <c r="D41">
-        <v>14.00045992241501</v>
+        <v>14.00773158057552</v>
       </c>
       <c r="E41">
-        <v>8.0184</v>
+        <v>8.263999999999999</v>
       </c>
       <c r="F41">
-        <v>9.5784</v>
+        <v>9.824</v>
       </c>
       <c r="G41">
         <v>10.9</v>
@@ -4649,28 +4649,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M41">
-        <v>0.55363152</v>
+        <v>0.5678272</v>
       </c>
       <c r="N41">
-        <v>1.764327663673469</v>
+        <v>1.750131983673469</v>
       </c>
       <c r="O41">
-        <v>0.2646491495510204</v>
+        <v>0.2625197975510204</v>
       </c>
       <c r="P41">
-        <v>1.499678514122449</v>
+        <v>1.487612186122449</v>
       </c>
       <c r="Q41">
-        <v>2.579678514122449</v>
+        <v>2.567612186122449</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1787766492614513</v>
+        <v>0.1807775370623405</v>
       </c>
       <c r="T41">
-        <v>1.593025993332208</v>
+        <v>1.616996113607166</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.186826616507437</v>
+        <v>4.082155951094752</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1281185222374043</v>
+        <v>0.1292423384253233</v>
       </c>
       <c r="C42">
-        <v>15.08373158057552</v>
+        <v>14.75341895399131</v>
       </c>
       <c r="D42">
-        <v>14.00773158057552</v>
+        <v>13.92301895399131</v>
       </c>
       <c r="E42">
-        <v>8.263999999999999</v>
+        <v>8.509599999999999</v>
       </c>
       <c r="F42">
-        <v>9.824</v>
+        <v>10.0696</v>
       </c>
       <c r="G42">
         <v>10.9</v>
@@ -4731,45 +4731,45 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M42">
-        <v>0.5678272</v>
+        <v>0.61726648</v>
       </c>
       <c r="N42">
-        <v>1.750131983673469</v>
+        <v>1.700692703673469</v>
       </c>
       <c r="O42">
-        <v>0.2625197975510204</v>
+        <v>0.2551039055510204</v>
       </c>
       <c r="P42">
-        <v>1.487612186122449</v>
+        <v>1.445588798122449</v>
       </c>
       <c r="Q42">
-        <v>2.567612186122449</v>
+        <v>2.525588798122449</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1807775370623405</v>
+        <v>0.1828462515683447</v>
       </c>
       <c r="T42">
-        <v>1.616996113607166</v>
+        <v>1.641778780332123</v>
       </c>
       <c r="U42">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V42">
         <v>0.15</v>
       </c>
       <c r="W42">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.082155951094752</v>
+        <v>3.755200158727993</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1292423384253233</v>
+        <v>0.1291761546132424</v>
       </c>
       <c r="C43">
-        <v>14.75341895399131</v>
+        <v>14.51277944821696</v>
       </c>
       <c r="D43">
-        <v>13.92301895399131</v>
+        <v>13.92797944821696</v>
       </c>
       <c r="E43">
-        <v>8.509599999999999</v>
+        <v>8.7552</v>
       </c>
       <c r="F43">
-        <v>10.0696</v>
+        <v>10.3152</v>
       </c>
       <c r="G43">
         <v>10.9</v>
@@ -4813,28 +4813,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M43">
-        <v>0.61726648</v>
+        <v>0.6323217600000001</v>
       </c>
       <c r="N43">
-        <v>1.700692703673469</v>
+        <v>1.685637423673469</v>
       </c>
       <c r="O43">
-        <v>0.2551039055510204</v>
+        <v>0.2528456135510204</v>
       </c>
       <c r="P43">
-        <v>1.445588798122449</v>
+        <v>1.432791810122449</v>
       </c>
       <c r="Q43">
-        <v>2.525588798122449</v>
+        <v>2.512791810122449</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1828462515683447</v>
+        <v>0.1849863010573145</v>
       </c>
       <c r="T43">
-        <v>1.641778780332123</v>
+        <v>1.667416021771733</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.755200158727993</v>
+        <v>3.665790631139231</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1291761546132424</v>
+        <v>0.1291099708011614</v>
       </c>
       <c r="C44">
-        <v>14.51277944821696</v>
+        <v>14.27214347835288</v>
       </c>
       <c r="D44">
-        <v>13.92797944821696</v>
+        <v>13.93294347835288</v>
       </c>
       <c r="E44">
-        <v>8.755199999999999</v>
+        <v>9.000799999999998</v>
       </c>
       <c r="F44">
-        <v>10.3152</v>
+        <v>10.5608</v>
       </c>
       <c r="G44">
         <v>10.9</v>
@@ -4895,28 +4895,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M44">
-        <v>0.63232176</v>
+        <v>0.64737704</v>
       </c>
       <c r="N44">
-        <v>1.685637423673469</v>
+        <v>1.67058214367347</v>
       </c>
       <c r="O44">
-        <v>0.2528456135510204</v>
+        <v>0.2505873215510204</v>
       </c>
       <c r="P44">
-        <v>1.432791810122449</v>
+        <v>1.419994822122449</v>
       </c>
       <c r="Q44">
-        <v>2.512791810122449</v>
+        <v>2.499994822122449</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1849863010573144</v>
+        <v>0.1872014400020376</v>
       </c>
       <c r="T44">
-        <v>1.667416021771733</v>
+        <v>1.693952815542557</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.665790631139231</v>
+        <v>3.580539686229017</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1291099708011614</v>
+        <v>0.1300909869890804</v>
       </c>
       <c r="C45">
-        <v>14.27214347835288</v>
+        <v>13.95332422822584</v>
       </c>
       <c r="D45">
-        <v>13.93294347835288</v>
+        <v>13.85972422822584</v>
       </c>
       <c r="E45">
-        <v>9.000799999999998</v>
+        <v>9.2464</v>
       </c>
       <c r="F45">
-        <v>10.5608</v>
+        <v>10.8064</v>
       </c>
       <c r="G45">
         <v>10.9</v>
@@ -4977,45 +4977,45 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M45">
-        <v>0.64737704</v>
+        <v>0.69269024</v>
       </c>
       <c r="N45">
-        <v>1.67058214367347</v>
+        <v>1.625268943673469</v>
       </c>
       <c r="O45">
-        <v>0.2505873215510204</v>
+        <v>0.2437903415510204</v>
       </c>
       <c r="P45">
-        <v>1.419994822122449</v>
+        <v>1.381478602122449</v>
       </c>
       <c r="Q45">
-        <v>2.499994822122449</v>
+        <v>2.461478602122449</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1872014400020376</v>
+        <v>0.1894956910519294</v>
       </c>
       <c r="T45">
-        <v>1.693952815542557</v>
+        <v>1.721437351948054</v>
       </c>
       <c r="U45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.15</v>
       </c>
       <c r="W45">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.580539686229017</v>
+        <v>3.346314196188861</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1300909869890804</v>
+        <v>0.1300486031769995</v>
       </c>
       <c r="C46">
-        <v>13.95332422822584</v>
+        <v>13.71087168262272</v>
       </c>
       <c r="D46">
-        <v>13.85972422822584</v>
+        <v>13.86287168262271</v>
       </c>
       <c r="E46">
-        <v>9.2464</v>
+        <v>9.491999999999999</v>
       </c>
       <c r="F46">
-        <v>10.8064</v>
+        <v>11.052</v>
       </c>
       <c r="G46">
         <v>10.9</v>
@@ -5059,28 +5059,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M46">
-        <v>0.69269024</v>
+        <v>0.7084332</v>
       </c>
       <c r="N46">
-        <v>1.625268943673469</v>
+        <v>1.609525983673469</v>
       </c>
       <c r="O46">
-        <v>0.2437903415510204</v>
+        <v>0.2414288975510204</v>
       </c>
       <c r="P46">
-        <v>1.381478602122449</v>
+        <v>1.368097086122449</v>
       </c>
       <c r="Q46">
-        <v>2.461478602122449</v>
+        <v>2.448097086122449</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1894956910519294</v>
+        <v>0.1918733694127263</v>
       </c>
       <c r="T46">
-        <v>1.721437351948054</v>
+        <v>1.749921326041024</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.346314196188861</v>
+        <v>3.271951658495776</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1300486031769995</v>
+        <v>0.1300062193649185</v>
       </c>
       <c r="C47">
-        <v>13.71087168262272</v>
+        <v>13.46842056687768</v>
       </c>
       <c r="D47">
-        <v>13.86287168262271</v>
+        <v>13.86602056687768</v>
       </c>
       <c r="E47">
-        <v>9.491999999999999</v>
+        <v>9.737599999999999</v>
       </c>
       <c r="F47">
-        <v>11.052</v>
+        <v>11.2976</v>
       </c>
       <c r="G47">
         <v>10.9</v>
@@ -5141,28 +5141,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M47">
-        <v>0.7084332</v>
+        <v>0.72417616</v>
       </c>
       <c r="N47">
-        <v>1.609525983673469</v>
+        <v>1.59378302367347</v>
       </c>
       <c r="O47">
-        <v>0.2414288975510204</v>
+        <v>0.2390674535510204</v>
       </c>
       <c r="P47">
-        <v>1.368097086122449</v>
+        <v>1.354715570122449</v>
       </c>
       <c r="Q47">
-        <v>2.448097086122449</v>
+        <v>2.434715570122449</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1918733694127263</v>
+        <v>0.1943391099350343</v>
       </c>
       <c r="T47">
-        <v>1.749921326041024</v>
+        <v>1.779460262137437</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.271951658495776</v>
+        <v>3.200822274615433</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1300062193649185</v>
+        <v>0.1299638355528376</v>
       </c>
       <c r="C48">
-        <v>13.46842056687768</v>
+        <v>13.22597088196531</v>
       </c>
       <c r="D48">
-        <v>13.86602056687768</v>
+        <v>13.86917088196531</v>
       </c>
       <c r="E48">
-        <v>9.737599999999999</v>
+        <v>9.9832</v>
       </c>
       <c r="F48">
-        <v>11.2976</v>
+        <v>11.5432</v>
       </c>
       <c r="G48">
         <v>10.9</v>
@@ -5223,28 +5223,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M48">
-        <v>0.72417616</v>
+        <v>0.73991912</v>
       </c>
       <c r="N48">
-        <v>1.59378302367347</v>
+        <v>1.578040063673469</v>
       </c>
       <c r="O48">
-        <v>0.2390674535510204</v>
+        <v>0.2367060095510204</v>
       </c>
       <c r="P48">
-        <v>1.354715570122449</v>
+        <v>1.341334054122449</v>
       </c>
       <c r="Q48">
-        <v>2.434715570122449</v>
+        <v>2.421334054122449</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1943391099350343</v>
+        <v>0.1968978972695048</v>
       </c>
       <c r="T48">
-        <v>1.779460262137437</v>
+        <v>1.810113875067677</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.200822274615433</v>
+        <v>3.13271967302787</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1299638355528376</v>
+        <v>0.1299214517407566</v>
       </c>
       <c r="C49">
-        <v>13.22597088196531</v>
+        <v>12.98352262886106</v>
       </c>
       <c r="D49">
-        <v>13.86917088196531</v>
+        <v>13.87232262886106</v>
       </c>
       <c r="E49">
-        <v>9.9832</v>
+        <v>10.2288</v>
       </c>
       <c r="F49">
-        <v>11.5432</v>
+        <v>11.7888</v>
       </c>
       <c r="G49">
         <v>10.9</v>
@@ -5305,28 +5305,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M49">
-        <v>0.73991912</v>
+        <v>0.75566208</v>
       </c>
       <c r="N49">
-        <v>1.578040063673469</v>
+        <v>1.562297103673469</v>
       </c>
       <c r="O49">
-        <v>0.2367060095510204</v>
+        <v>0.2343445655510204</v>
       </c>
       <c r="P49">
-        <v>1.341334054122449</v>
+        <v>1.327952538122449</v>
       </c>
       <c r="Q49">
-        <v>2.421334054122449</v>
+        <v>2.407952538122449</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1968978972695048</v>
+        <v>0.199555099501455</v>
       </c>
       <c r="T49">
-        <v>1.810113875067677</v>
+        <v>1.841946473110618</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.13271967302787</v>
+        <v>3.067454679839789</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1299214517407566</v>
+        <v>0.1298790679286756</v>
       </c>
       <c r="C50">
-        <v>12.98352262886106</v>
+        <v>12.74107580854129</v>
       </c>
       <c r="D50">
-        <v>13.87232262886106</v>
+        <v>13.8754758085413</v>
       </c>
       <c r="E50">
-        <v>10.2288</v>
+        <v>10.4744</v>
       </c>
       <c r="F50">
-        <v>11.7888</v>
+        <v>12.0344</v>
       </c>
       <c r="G50">
         <v>10.9</v>
@@ -5387,28 +5387,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M50">
-        <v>0.7556620799999999</v>
+        <v>0.77140504</v>
       </c>
       <c r="N50">
-        <v>1.562297103673469</v>
+        <v>1.54655414367347</v>
       </c>
       <c r="O50">
-        <v>0.2343445655510204</v>
+        <v>0.2319831215510204</v>
       </c>
       <c r="P50">
-        <v>1.327952538122449</v>
+        <v>1.314571022122449</v>
       </c>
       <c r="Q50">
-        <v>2.407952538122449</v>
+        <v>2.394571022122449</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.199555099501455</v>
+        <v>0.2023165057425012</v>
       </c>
       <c r="T50">
-        <v>1.841946473110618</v>
+        <v>1.875027408331714</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.06745467983979</v>
+        <v>3.004853563924692</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1298790679286756</v>
+        <v>0.1331516841165947</v>
       </c>
       <c r="C51">
-        <v>12.74107580854129</v>
+        <v>12.2561517153791</v>
       </c>
       <c r="D51">
-        <v>13.8754758085413</v>
+        <v>13.6361517153791</v>
       </c>
       <c r="E51">
-        <v>10.4744</v>
+        <v>10.72</v>
       </c>
       <c r="F51">
-        <v>12.0344</v>
+        <v>12.28</v>
       </c>
       <c r="G51">
         <v>10.9</v>
@@ -5469,45 +5469,45 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M51">
-        <v>0.77140504</v>
+        <v>0.8829320000000001</v>
       </c>
       <c r="N51">
-        <v>1.54655414367347</v>
+        <v>1.435027183673469</v>
       </c>
       <c r="O51">
-        <v>0.2319831215510204</v>
+        <v>0.2152540775510204</v>
       </c>
       <c r="P51">
-        <v>1.314571022122449</v>
+        <v>1.219773106122449</v>
       </c>
       <c r="Q51">
-        <v>2.394571022122449</v>
+        <v>2.299773106122449</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2023165057425012</v>
+        <v>0.2051883682331893</v>
       </c>
       <c r="T51">
-        <v>1.875027408331714</v>
+        <v>1.909431580961654</v>
       </c>
       <c r="U51">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V51">
         <v>0.15</v>
       </c>
       <c r="W51">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.004853563924692</v>
+        <v>2.625297512915456</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1331516841165947</v>
+        <v>0.1331756003045137</v>
       </c>
       <c r="C52">
-        <v>12.2561517153791</v>
+        <v>12.00883312448491</v>
       </c>
       <c r="D52">
-        <v>13.6361517153791</v>
+        <v>13.63443312448491</v>
       </c>
       <c r="E52">
-        <v>10.72</v>
+        <v>10.9656</v>
       </c>
       <c r="F52">
-        <v>12.28</v>
+        <v>12.5256</v>
       </c>
       <c r="G52">
         <v>10.9</v>
@@ -5551,28 +5551,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M52">
-        <v>0.8829320000000001</v>
+        <v>0.90059064</v>
       </c>
       <c r="N52">
-        <v>1.435027183673469</v>
+        <v>1.41736854367347</v>
       </c>
       <c r="O52">
-        <v>0.2152540775510204</v>
+        <v>0.2126052815510204</v>
       </c>
       <c r="P52">
-        <v>1.219773106122449</v>
+        <v>1.204763262122449</v>
       </c>
       <c r="Q52">
-        <v>2.299773106122449</v>
+        <v>2.284763262122449</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2051883682331893</v>
+        <v>0.2081774496010484</v>
       </c>
       <c r="T52">
-        <v>1.909431580961654</v>
+        <v>1.945240005535672</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.625297512915456</v>
+        <v>2.573821091093584</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1331756003045137</v>
+        <v>0.1331995164924327</v>
       </c>
       <c r="C53">
-        <v>12.00883312448491</v>
+        <v>11.76151496673088</v>
       </c>
       <c r="D53">
-        <v>13.63443312448491</v>
+        <v>13.63271496673088</v>
       </c>
       <c r="E53">
-        <v>10.9656</v>
+        <v>11.2112</v>
       </c>
       <c r="F53">
-        <v>12.5256</v>
+        <v>12.7712</v>
       </c>
       <c r="G53">
         <v>10.9</v>
@@ -5633,28 +5633,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M53">
-        <v>0.90059064</v>
+        <v>0.9182492800000001</v>
       </c>
       <c r="N53">
-        <v>1.41736854367347</v>
+        <v>1.399709903673469</v>
       </c>
       <c r="O53">
-        <v>0.2126052815510204</v>
+        <v>0.2099564855510204</v>
       </c>
       <c r="P53">
-        <v>1.204763262122449</v>
+        <v>1.189753418122449</v>
       </c>
       <c r="Q53">
-        <v>2.284763262122449</v>
+        <v>2.269753418122449</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2081774496010484</v>
+        <v>0.2112910760259015</v>
       </c>
       <c r="T53">
-        <v>1.945240005535672</v>
+        <v>1.982540447800275</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.573821091093584</v>
+        <v>2.524324531649477</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1331995164924327</v>
+        <v>0.1349803826803518</v>
       </c>
       <c r="C54">
-        <v>11.76151496673088</v>
+        <v>11.38918146616339</v>
       </c>
       <c r="D54">
-        <v>13.63271496673088</v>
+        <v>13.50598146616339</v>
       </c>
       <c r="E54">
-        <v>11.2112</v>
+        <v>11.4568</v>
       </c>
       <c r="F54">
-        <v>12.7712</v>
+        <v>13.0168</v>
       </c>
       <c r="G54">
         <v>10.9</v>
@@ -5715,45 +5715,45 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M54">
-        <v>0.9182492800000001</v>
+        <v>0.9866734400000001</v>
       </c>
       <c r="N54">
-        <v>1.399709903673469</v>
+        <v>1.331285743673469</v>
       </c>
       <c r="O54">
-        <v>0.2099564855510204</v>
+        <v>0.1996928615510204</v>
       </c>
       <c r="P54">
-        <v>1.189753418122449</v>
+        <v>1.131592882122449</v>
       </c>
       <c r="Q54">
-        <v>2.269753418122449</v>
+        <v>2.211592882122449</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2112910760259015</v>
+        <v>0.2145371971922378</v>
       </c>
       <c r="T54">
-        <v>1.982540447800275</v>
+        <v>2.021428142927202</v>
       </c>
       <c r="U54">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
         <v>0.15</v>
       </c>
       <c r="W54">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.524324531649477</v>
+        <v>2.349266829026501</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1349803826803518</v>
+        <v>0.1350374488682708</v>
       </c>
       <c r="C55">
-        <v>11.38918146616339</v>
+        <v>11.13955936076809</v>
       </c>
       <c r="D55">
-        <v>13.50598146616339</v>
+        <v>13.50195936076809</v>
       </c>
       <c r="E55">
-        <v>11.4568</v>
+        <v>11.7024</v>
       </c>
       <c r="F55">
-        <v>13.0168</v>
+        <v>13.2624</v>
       </c>
       <c r="G55">
         <v>10.9</v>
@@ -5797,28 +5797,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M55">
-        <v>0.9866734400000001</v>
+        <v>1.00528992</v>
       </c>
       <c r="N55">
-        <v>1.331285743673469</v>
+        <v>1.312669263673469</v>
       </c>
       <c r="O55">
-        <v>0.1996928615510204</v>
+        <v>0.1969003895510204</v>
       </c>
       <c r="P55">
-        <v>1.131592882122449</v>
+        <v>1.115768874122449</v>
       </c>
       <c r="Q55">
-        <v>2.211592882122449</v>
+        <v>2.195768874122449</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2145371971922378</v>
+        <v>0.2179244540614583</v>
       </c>
       <c r="T55">
-        <v>2.021428142927202</v>
+        <v>2.062006607407473</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.349266829026501</v>
+        <v>2.305761887748232</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1350374488682708</v>
+        <v>0.1350945150561898</v>
       </c>
       <c r="C56">
-        <v>11.13955936076809</v>
+        <v>10.88993965023994</v>
       </c>
       <c r="D56">
-        <v>13.50195936076809</v>
+        <v>13.49793965023994</v>
       </c>
       <c r="E56">
-        <v>11.7024</v>
+        <v>11.948</v>
       </c>
       <c r="F56">
-        <v>13.2624</v>
+        <v>13.508</v>
       </c>
       <c r="G56">
         <v>10.9</v>
@@ -5879,28 +5879,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M56">
-        <v>1.00528992</v>
+        <v>1.0239064</v>
       </c>
       <c r="N56">
-        <v>1.312669263673469</v>
+        <v>1.294052783673469</v>
       </c>
       <c r="O56">
-        <v>0.1969003895510204</v>
+        <v>0.1941079175510204</v>
       </c>
       <c r="P56">
-        <v>1.115768874122449</v>
+        <v>1.099944866122449</v>
       </c>
       <c r="Q56">
-        <v>2.195768874122449</v>
+        <v>2.179944866122449</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2179244540614583</v>
+        <v>0.2214622556804219</v>
       </c>
       <c r="T56">
-        <v>2.062006607407473</v>
+        <v>2.104388559197979</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.305761887748232</v>
+        <v>2.263838944334628</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1350945150561898</v>
+        <v>0.1351515812441089</v>
       </c>
       <c r="C57">
-        <v>10.88993965023994</v>
+        <v>10.64032233244062</v>
       </c>
       <c r="D57">
-        <v>13.49793965023994</v>
+        <v>13.49392233244062</v>
       </c>
       <c r="E57">
-        <v>11.948</v>
+        <v>12.1936</v>
       </c>
       <c r="F57">
-        <v>13.508</v>
+        <v>13.7536</v>
       </c>
       <c r="G57">
         <v>10.9</v>
@@ -5961,28 +5961,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M57">
-        <v>1.0239064</v>
+        <v>1.04252288</v>
       </c>
       <c r="N57">
-        <v>1.294052783673469</v>
+        <v>1.275436303673469</v>
       </c>
       <c r="O57">
-        <v>0.1941079175510204</v>
+        <v>0.1913154455510204</v>
       </c>
       <c r="P57">
-        <v>1.099944866122449</v>
+        <v>1.084120858122449</v>
       </c>
       <c r="Q57">
-        <v>2.179944866122449</v>
+        <v>2.164120858122449</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2214622556804219</v>
+        <v>0.2251608664638838</v>
       </c>
       <c r="T57">
-        <v>2.104388559197979</v>
+        <v>2.148696963342598</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.263838944334628</v>
+        <v>2.223413248900081</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1351515812441089</v>
+        <v>0.1352086474320279</v>
       </c>
       <c r="C58">
-        <v>10.64032233244062</v>
+        <v>10.39070740523435</v>
       </c>
       <c r="D58">
-        <v>13.49392233244062</v>
+        <v>13.48990740523435</v>
       </c>
       <c r="E58">
-        <v>12.1936</v>
+        <v>12.4392</v>
       </c>
       <c r="F58">
-        <v>13.7536</v>
+        <v>13.9992</v>
       </c>
       <c r="G58">
         <v>10.9</v>
@@ -6043,28 +6043,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M58">
-        <v>1.04252288</v>
+        <v>1.06113936</v>
       </c>
       <c r="N58">
-        <v>1.275436303673469</v>
+        <v>1.256819823673469</v>
       </c>
       <c r="O58">
-        <v>0.1913154455510204</v>
+        <v>0.1885229735510204</v>
       </c>
       <c r="P58">
-        <v>1.084120858122449</v>
+        <v>1.068296850122449</v>
       </c>
       <c r="Q58">
-        <v>2.164120858122449</v>
+        <v>2.148296850122449</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2251608664638838</v>
+        <v>0.2290315056558789</v>
       </c>
       <c r="T58">
-        <v>2.148696963342598</v>
+        <v>2.195066223493944</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.223413248900081</v>
+        <v>2.184405998919378</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1352086474320279</v>
+        <v>0.135265713619947</v>
       </c>
       <c r="C59">
-        <v>10.39070740523435</v>
+        <v>10.14109486648791</v>
       </c>
       <c r="D59">
-        <v>13.48990740523435</v>
+        <v>13.48589486648791</v>
       </c>
       <c r="E59">
-        <v>12.4392</v>
+        <v>12.6848</v>
       </c>
       <c r="F59">
-        <v>13.9992</v>
+        <v>14.2448</v>
       </c>
       <c r="G59">
         <v>10.9</v>
@@ -6125,28 +6125,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M59">
-        <v>1.06113936</v>
+        <v>1.07975584</v>
       </c>
       <c r="N59">
-        <v>1.256819823673469</v>
+        <v>1.238203343673469</v>
       </c>
       <c r="O59">
-        <v>0.1885229735510204</v>
+        <v>0.1857305015510204</v>
       </c>
       <c r="P59">
-        <v>1.068296850122449</v>
+        <v>1.052472842122449</v>
       </c>
       <c r="Q59">
-        <v>2.148296850122449</v>
+        <v>2.132472842122449</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2290315056558789</v>
+        <v>0.2330864609998737</v>
       </c>
       <c r="T59">
-        <v>2.195066223493944</v>
+        <v>2.243643543652497</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.184405998919378</v>
+        <v>2.146743826524216</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1352657136199469</v>
+        <v>0.135322779807866</v>
       </c>
       <c r="C60">
-        <v>10.14109486648792</v>
+        <v>9.891484714070616</v>
       </c>
       <c r="D60">
-        <v>13.48589486648791</v>
+        <v>13.48188471407062</v>
       </c>
       <c r="E60">
-        <v>12.6848</v>
+        <v>12.9304</v>
       </c>
       <c r="F60">
-        <v>14.2448</v>
+        <v>14.4904</v>
       </c>
       <c r="G60">
         <v>10.9</v>
@@ -6207,28 +6207,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M60">
-        <v>1.07975584</v>
+        <v>1.09837232</v>
       </c>
       <c r="N60">
-        <v>1.238203343673469</v>
+        <v>1.219586863673469</v>
       </c>
       <c r="O60">
-        <v>0.1857305015510204</v>
+        <v>0.1829380295510204</v>
       </c>
       <c r="P60">
-        <v>1.052472842122449</v>
+        <v>1.036648834122449</v>
       </c>
       <c r="Q60">
-        <v>2.132472842122449</v>
+        <v>2.116648834122449</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2330864609998737</v>
+        <v>0.2373392190435755</v>
       </c>
       <c r="T60">
-        <v>2.243643543652496</v>
+        <v>2.294590489184637</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.146743826524216</v>
+        <v>2.11035833793906</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.135322779807866</v>
+        <v>0.135379845995785</v>
       </c>
       <c r="C61">
-        <v>9.891484714070616</v>
+        <v>9.641876945854309</v>
       </c>
       <c r="D61">
-        <v>13.48188471407062</v>
+        <v>13.47787694585431</v>
       </c>
       <c r="E61">
-        <v>12.9304</v>
+        <v>13.176</v>
       </c>
       <c r="F61">
-        <v>14.4904</v>
+        <v>14.736</v>
       </c>
       <c r="G61">
         <v>10.9</v>
@@ -6289,28 +6289,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M61">
-        <v>1.09837232</v>
+        <v>1.1169888</v>
       </c>
       <c r="N61">
-        <v>1.219586863673469</v>
+        <v>1.200970383673469</v>
       </c>
       <c r="O61">
-        <v>0.1829380295510204</v>
+        <v>0.1801455575510204</v>
       </c>
       <c r="P61">
-        <v>1.036648834122449</v>
+        <v>1.020824826122449</v>
       </c>
       <c r="Q61">
-        <v>2.116648834122449</v>
+        <v>2.100824826122449</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2373392190435755</v>
+        <v>0.2418046149894625</v>
       </c>
       <c r="T61">
-        <v>2.294590489184637</v>
+        <v>2.348084781993384</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.11035833793906</v>
+        <v>2.075185698973409</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.135379845995785</v>
+        <v>0.135436912183704</v>
       </c>
       <c r="C62">
-        <v>9.641876945854309</v>
+        <v>9.392271559713352</v>
       </c>
       <c r="D62">
-        <v>13.47787694585431</v>
+        <v>13.47387155971335</v>
       </c>
       <c r="E62">
-        <v>13.176</v>
+        <v>13.4216</v>
       </c>
       <c r="F62">
-        <v>14.736</v>
+        <v>14.9816</v>
       </c>
       <c r="G62">
         <v>10.9</v>
@@ -6371,28 +6371,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M62">
-        <v>1.1169888</v>
+        <v>1.13560528</v>
       </c>
       <c r="N62">
-        <v>1.200970383673469</v>
+        <v>1.182353903673469</v>
       </c>
       <c r="O62">
-        <v>0.1801455575510204</v>
+        <v>0.1773530855510204</v>
       </c>
       <c r="P62">
-        <v>1.020824826122449</v>
+        <v>1.005000818122449</v>
       </c>
       <c r="Q62">
-        <v>2.100824826122449</v>
+        <v>2.085000818122449</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2418046149894625</v>
+        <v>0.2464990055992411</v>
       </c>
       <c r="T62">
-        <v>2.348084781993384</v>
+        <v>2.404322371869247</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.075185698973409</v>
+        <v>2.04116626128532</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.135436912183704</v>
+        <v>0.1354939783716231</v>
       </c>
       <c r="C63">
-        <v>9.392271559713352</v>
+        <v>9.142668553524654</v>
       </c>
       <c r="D63">
-        <v>13.47387155971335</v>
+        <v>13.46986855352465</v>
       </c>
       <c r="E63">
-        <v>13.4216</v>
+        <v>13.6672</v>
       </c>
       <c r="F63">
-        <v>14.9816</v>
+        <v>15.2272</v>
       </c>
       <c r="G63">
         <v>10.9</v>
@@ -6453,28 +6453,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M63">
-        <v>1.13560528</v>
+        <v>1.15422176</v>
       </c>
       <c r="N63">
-        <v>1.182353903673469</v>
+        <v>1.163737423673469</v>
       </c>
       <c r="O63">
-        <v>0.1773530855510204</v>
+        <v>0.1745606135510204</v>
       </c>
       <c r="P63">
-        <v>1.005000818122449</v>
+        <v>0.9891768101224491</v>
       </c>
       <c r="Q63">
-        <v>2.085000818122449</v>
+        <v>2.069176810122449</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2464990055992411</v>
+        <v>0.2514404693990081</v>
       </c>
       <c r="T63">
-        <v>2.404322371869247</v>
+        <v>2.463519834896472</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.04116626128532</v>
+        <v>2.008244224812977</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1354939783716231</v>
+        <v>0.1431551445595421</v>
       </c>
       <c r="C64">
-        <v>9.142668553524654</v>
+        <v>8.380428690416444</v>
       </c>
       <c r="D64">
-        <v>13.46986855352465</v>
+        <v>12.95322869041645</v>
       </c>
       <c r="E64">
-        <v>13.6672</v>
+        <v>13.9128</v>
       </c>
       <c r="F64">
-        <v>15.2272</v>
+        <v>15.4728</v>
       </c>
       <c r="G64">
         <v>10.9</v>
@@ -6535,45 +6535,45 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M64">
-        <v>1.15422176</v>
+        <v>1.392552</v>
       </c>
       <c r="N64">
-        <v>1.163737423673469</v>
+        <v>0.9254071836734696</v>
       </c>
       <c r="O64">
-        <v>0.1745606135510204</v>
+        <v>0.1388110775510204</v>
       </c>
       <c r="P64">
-        <v>0.9891768101224491</v>
+        <v>0.7865961061224492</v>
       </c>
       <c r="Q64">
-        <v>2.069176810122449</v>
+        <v>1.866596106122449</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2514404693990081</v>
+        <v>0.2566490393501139</v>
       </c>
       <c r="T64">
-        <v>2.463519834896472</v>
+        <v>2.525917160790033</v>
       </c>
       <c r="U64">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V64">
         <v>0.15</v>
       </c>
       <c r="W64">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.008244224812977</v>
+        <v>1.664540486583962</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1431551445595421</v>
+        <v>0.1433329107474612</v>
       </c>
       <c r="C65">
-        <v>8.380428690416444</v>
+        <v>8.123310864137121</v>
       </c>
       <c r="D65">
-        <v>12.95322869041645</v>
+        <v>12.94171086413712</v>
       </c>
       <c r="E65">
-        <v>13.9128</v>
+        <v>14.1584</v>
       </c>
       <c r="F65">
-        <v>15.4728</v>
+        <v>15.7184</v>
       </c>
       <c r="G65">
         <v>10.9</v>
@@ -6617,28 +6617,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M65">
-        <v>1.392552</v>
+        <v>1.414656</v>
       </c>
       <c r="N65">
-        <v>0.9254071836734696</v>
+        <v>0.9033031836734695</v>
       </c>
       <c r="O65">
-        <v>0.1388110775510204</v>
+        <v>0.1354954775510204</v>
       </c>
       <c r="P65">
-        <v>0.7865961061224492</v>
+        <v>0.7678077061224491</v>
       </c>
       <c r="Q65">
-        <v>1.866596106122449</v>
+        <v>1.847807706122449</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2566490393501139</v>
+        <v>0.2621469742985032</v>
       </c>
       <c r="T65">
-        <v>2.525917160790033</v>
+        <v>2.591781004788791</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.664540486583962</v>
+        <v>1.638532041481088</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1433329107474612</v>
+        <v>0.1435106769353802</v>
       </c>
       <c r="C66">
-        <v>8.123310864137121</v>
+        <v>7.866213502634649</v>
       </c>
       <c r="D66">
-        <v>12.94171086413712</v>
+        <v>12.93021350263465</v>
       </c>
       <c r="E66">
-        <v>14.1584</v>
+        <v>14.404</v>
       </c>
       <c r="F66">
-        <v>15.7184</v>
+        <v>15.964</v>
       </c>
       <c r="G66">
         <v>10.9</v>
@@ -6699,28 +6699,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M66">
-        <v>1.414656</v>
+        <v>1.43676</v>
       </c>
       <c r="N66">
-        <v>0.9033031836734695</v>
+        <v>0.8811991836734694</v>
       </c>
       <c r="O66">
-        <v>0.1354954775510204</v>
+        <v>0.1321798775510204</v>
       </c>
       <c r="P66">
-        <v>0.7678077061224491</v>
+        <v>0.749019306122449</v>
       </c>
       <c r="Q66">
-        <v>1.847807706122449</v>
+        <v>1.829019306122449</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2621469742985032</v>
+        <v>0.2679590769582292</v>
       </c>
       <c r="T66">
-        <v>2.591781004788791</v>
+        <v>2.66140849701605</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.638532041481088</v>
+        <v>1.613323856227532</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1435106769353802</v>
+        <v>0.1436884431232992</v>
       </c>
       <c r="C67">
-        <v>7.866213502634649</v>
+        <v>7.609136551414981</v>
       </c>
       <c r="D67">
-        <v>12.93021350263465</v>
+        <v>12.91873655141498</v>
       </c>
       <c r="E67">
-        <v>14.404</v>
+        <v>14.6496</v>
       </c>
       <c r="F67">
-        <v>15.964</v>
+        <v>16.2096</v>
       </c>
       <c r="G67">
         <v>10.9</v>
@@ -6781,28 +6781,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M67">
-        <v>1.43676</v>
+        <v>1.458864</v>
       </c>
       <c r="N67">
-        <v>0.8811991836734694</v>
+        <v>0.8590951836734697</v>
       </c>
       <c r="O67">
-        <v>0.1321798775510204</v>
+        <v>0.1288642775510205</v>
       </c>
       <c r="P67">
-        <v>0.749019306122449</v>
+        <v>0.7302309061224492</v>
       </c>
       <c r="Q67">
-        <v>1.829019306122449</v>
+        <v>1.810230906122449</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2679590769582292</v>
+        <v>0.2741130680097036</v>
       </c>
       <c r="T67">
-        <v>2.66140849701605</v>
+        <v>2.735131724080207</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.613323856227532</v>
+        <v>1.5888795553756</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1436884431232992</v>
+        <v>0.1438662093112182</v>
       </c>
       <c r="C68">
-        <v>7.609136551414981</v>
+        <v>7.352079956177356</v>
       </c>
       <c r="D68">
-        <v>12.91873655141498</v>
+        <v>12.90727995617736</v>
       </c>
       <c r="E68">
-        <v>14.6496</v>
+        <v>14.8952</v>
       </c>
       <c r="F68">
-        <v>16.2096</v>
+        <v>16.4552</v>
       </c>
       <c r="G68">
         <v>10.9</v>
@@ -6863,28 +6863,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M68">
-        <v>1.458864</v>
+        <v>1.480968</v>
       </c>
       <c r="N68">
-        <v>0.8590951836734697</v>
+        <v>0.8369911836734694</v>
       </c>
       <c r="O68">
-        <v>0.1288642775510205</v>
+        <v>0.1255486775510204</v>
       </c>
       <c r="P68">
-        <v>0.7302309061224492</v>
+        <v>0.711442506122449</v>
       </c>
       <c r="Q68">
-        <v>1.810230906122449</v>
+        <v>1.791442506122449</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2741130680097036</v>
+        <v>0.2806400282158129</v>
       </c>
       <c r="T68">
-        <v>2.735131724080207</v>
+        <v>2.813323025511888</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.5888795553756</v>
+        <v>1.565164935146113</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1438662093112182</v>
+        <v>0.1440439754991373</v>
       </c>
       <c r="C69">
-        <v>7.352079956177356</v>
+        <v>7.095043662813488</v>
       </c>
       <c r="D69">
-        <v>12.90727995617736</v>
+        <v>12.89584366281349</v>
       </c>
       <c r="E69">
-        <v>14.8952</v>
+        <v>15.1408</v>
       </c>
       <c r="F69">
-        <v>16.4552</v>
+        <v>16.7008</v>
       </c>
       <c r="G69">
         <v>10.9</v>
@@ -6945,28 +6945,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M69">
-        <v>1.480968</v>
+        <v>1.503072</v>
       </c>
       <c r="N69">
-        <v>0.8369911836734694</v>
+        <v>0.8148871836734695</v>
       </c>
       <c r="O69">
-        <v>0.1255486775510204</v>
+        <v>0.1222330775510204</v>
       </c>
       <c r="P69">
-        <v>0.711442506122449</v>
+        <v>0.692654106122449</v>
       </c>
       <c r="Q69">
-        <v>1.791442506122449</v>
+        <v>1.772654106122449</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2806400282158129</v>
+        <v>0.2875749234348041</v>
       </c>
       <c r="T69">
-        <v>2.813323025511888</v>
+        <v>2.896401283283049</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.565164935146113</v>
+        <v>1.542147803746906</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1440439754991373</v>
+        <v>0.1442217416870563</v>
       </c>
       <c r="C70">
-        <v>7.095043662813488</v>
+        <v>6.838027617406674</v>
       </c>
       <c r="D70">
-        <v>12.89584366281349</v>
+        <v>12.88442761740667</v>
       </c>
       <c r="E70">
-        <v>15.1408</v>
+        <v>15.3864</v>
       </c>
       <c r="F70">
-        <v>16.7008</v>
+        <v>16.9464</v>
       </c>
       <c r="G70">
         <v>10.9</v>
@@ -7027,28 +7027,28 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M70">
-        <v>1.503072</v>
+        <v>1.525176</v>
       </c>
       <c r="N70">
-        <v>0.8148871836734695</v>
+        <v>0.7927831836734693</v>
       </c>
       <c r="O70">
-        <v>0.1222330775510204</v>
+        <v>0.1189174775510204</v>
       </c>
       <c r="P70">
-        <v>0.692654106122449</v>
+        <v>0.6738657061224489</v>
       </c>
       <c r="Q70">
-        <v>1.772654106122449</v>
+        <v>1.753865706122449</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2875749234348041</v>
+        <v>0.2949572312485689</v>
       </c>
       <c r="T70">
-        <v>2.896401283283049</v>
+        <v>2.98483942865235</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.542147803746906</v>
+        <v>1.519797835576661</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1442217416870563</v>
+        <v>0.1801903641931492</v>
       </c>
       <c r="C71">
-        <v>6.838027617406674</v>
+        <v>4.635168921096607</v>
       </c>
       <c r="D71">
-        <v>12.88442761740667</v>
+        <v>10.92716892109661</v>
       </c>
       <c r="E71">
-        <v>15.3864</v>
+        <v>15.632</v>
       </c>
       <c r="F71">
-        <v>16.9464</v>
+        <v>17.192</v>
       </c>
       <c r="G71">
         <v>10.9</v>
@@ -7109,45 +7109,45 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M71">
-        <v>1.525176</v>
+        <v>2.5237856</v>
       </c>
       <c r="N71">
-        <v>0.7927831836734693</v>
+        <v>-0.2058264163265306</v>
       </c>
       <c r="O71">
-        <v>0.1189174775510204</v>
+        <v>-0.03087396244897959</v>
       </c>
       <c r="P71">
-        <v>0.6738657061224489</v>
+        <v>-0.174952453877551</v>
       </c>
       <c r="Q71">
-        <v>1.753865706122449</v>
+        <v>0.905047546122449</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2949572312485689</v>
+        <v>0.3052909367718192</v>
       </c>
       <c r="T71">
-        <v>2.98483942865235</v>
+        <v>3.10863455807851</v>
       </c>
       <c r="U71">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.15</v>
+        <v>0.1377668045776236</v>
       </c>
       <c r="W71">
-        <v>0.0765</v>
+        <v>0.1265758330880049</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.519797835576661</v>
+        <v>0.9184453638508236</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1801903641931492</v>
+        <v>0.1812003641931492</v>
       </c>
       <c r="C72">
-        <v>4.635168921096607</v>
+        <v>4.343155910820609</v>
       </c>
       <c r="D72">
-        <v>10.92716892109661</v>
+        <v>10.88075591082061</v>
       </c>
       <c r="E72">
-        <v>15.632</v>
+        <v>15.8776</v>
       </c>
       <c r="F72">
-        <v>17.192</v>
+        <v>17.4376</v>
       </c>
       <c r="G72">
         <v>10.9</v>
@@ -7191,37 +7191,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M72">
-        <v>2.5237856</v>
+        <v>2.55983968</v>
       </c>
       <c r="N72">
-        <v>-0.2058264163265306</v>
+        <v>-0.2418804963265306</v>
       </c>
       <c r="O72">
-        <v>-0.03087396244897959</v>
+        <v>-0.03628207444897959</v>
       </c>
       <c r="P72">
-        <v>-0.174952453877551</v>
+        <v>-0.205598421877551</v>
       </c>
       <c r="Q72">
-        <v>0.905047546122449</v>
+        <v>0.874401578122449</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3052909367718192</v>
+        <v>0.3142389001087785</v>
       </c>
       <c r="T72">
-        <v>3.10863455807851</v>
+        <v>3.215828853184666</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.1377668045776236</v>
+        <v>0.1358264270483612</v>
       </c>
       <c r="W72">
-        <v>0.1265758330880049</v>
+        <v>0.1268606805093006</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.9184453638508236</v>
+        <v>0.9055095136557416</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1812003641931492</v>
+        <v>0.1822103641931492</v>
       </c>
       <c r="C73">
-        <v>4.343155910820609</v>
+        <v>4.051535510275208</v>
       </c>
       <c r="D73">
-        <v>10.88075591082061</v>
+        <v>10.83473551027521</v>
       </c>
       <c r="E73">
-        <v>15.8776</v>
+        <v>16.1232</v>
       </c>
       <c r="F73">
-        <v>17.4376</v>
+        <v>17.6832</v>
       </c>
       <c r="G73">
         <v>10.9</v>
@@ -7273,37 +7273,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M73">
-        <v>2.55983968</v>
+        <v>2.59589376</v>
       </c>
       <c r="N73">
-        <v>-0.2418804963265306</v>
+        <v>-0.2779345763265306</v>
       </c>
       <c r="O73">
-        <v>-0.03628207444897959</v>
+        <v>-0.04169018644897959</v>
       </c>
       <c r="P73">
-        <v>-0.205598421877551</v>
+        <v>-0.236244389877551</v>
       </c>
       <c r="Q73">
-        <v>0.874401578122449</v>
+        <v>0.843755610122449</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3142389001087785</v>
+        <v>0.323826003684092</v>
       </c>
       <c r="T73">
-        <v>3.215828853184665</v>
+        <v>3.330679883655546</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.1358264270483612</v>
+        <v>0.1339399488949118</v>
       </c>
       <c r="W73">
-        <v>0.1268606805093006</v>
+        <v>0.127137615502227</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.9055095136557416</v>
+        <v>0.8929329926327453</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1822103641931492</v>
+        <v>0.1832203641931492</v>
       </c>
       <c r="C74">
-        <v>4.051535510275208</v>
+        <v>3.760302758786768</v>
       </c>
       <c r="D74">
-        <v>10.83473551027521</v>
+        <v>10.78910275878676</v>
       </c>
       <c r="E74">
-        <v>16.1232</v>
+        <v>16.3688</v>
       </c>
       <c r="F74">
-        <v>17.6832</v>
+        <v>17.9288</v>
       </c>
       <c r="G74">
         <v>10.9</v>
@@ -7355,37 +7355,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M74">
-        <v>2.59589376</v>
+        <v>2.63194784</v>
       </c>
       <c r="N74">
-        <v>-0.2779345763265306</v>
+        <v>-0.3139886563265306</v>
       </c>
       <c r="O74">
-        <v>-0.04169018644897959</v>
+        <v>-0.04709829844897959</v>
       </c>
       <c r="P74">
-        <v>-0.236244389877551</v>
+        <v>-0.266890357877551</v>
       </c>
       <c r="Q74">
-        <v>0.843755610122449</v>
+        <v>0.8131096421224491</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.323826003684092</v>
+        <v>0.3341232630797991</v>
       </c>
       <c r="T74">
-        <v>3.330679883655546</v>
+        <v>3.45403839786501</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.1339399488949118</v>
+        <v>0.1321051550744335</v>
       </c>
       <c r="W74">
-        <v>0.127137615502227</v>
+        <v>0.1274069632350732</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8929329926327453</v>
+        <v>0.880701033829557</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1832203641931492</v>
+        <v>0.1842303641931491</v>
       </c>
       <c r="C75">
-        <v>3.760302758786768</v>
+        <v>3.469452778902799</v>
       </c>
       <c r="D75">
-        <v>10.78910275878676</v>
+        <v>10.7438527789028</v>
       </c>
       <c r="E75">
-        <v>16.3688</v>
+        <v>16.6144</v>
       </c>
       <c r="F75">
-        <v>17.9288</v>
+        <v>18.1744</v>
       </c>
       <c r="G75">
         <v>10.9</v>
@@ -7437,37 +7437,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M75">
-        <v>2.63194784</v>
+        <v>2.66800192</v>
       </c>
       <c r="N75">
-        <v>-0.3139886563265306</v>
+        <v>-0.3500427363265306</v>
       </c>
       <c r="O75">
-        <v>-0.04709829844897959</v>
+        <v>-0.05250641044897959</v>
       </c>
       <c r="P75">
-        <v>-0.266890357877551</v>
+        <v>-0.297536325877551</v>
       </c>
       <c r="Q75">
-        <v>0.8131096421224491</v>
+        <v>0.7824636741224491</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3341232630797991</v>
+        <v>0.345212619352099</v>
       </c>
       <c r="T75">
-        <v>3.45403839786501</v>
+        <v>3.586886028552126</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1321051550744335</v>
+        <v>0.1303199502761304</v>
       </c>
       <c r="W75">
-        <v>0.1274069632350732</v>
+        <v>0.1276690312994641</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.880701033829557</v>
+        <v>0.8687996685075359</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1842303641931491</v>
+        <v>0.1852403641931492</v>
       </c>
       <c r="C76">
-        <v>3.469452778902799</v>
+        <v>3.178980774654089</v>
       </c>
       <c r="D76">
-        <v>10.7438527789028</v>
+        <v>10.69898077465409</v>
       </c>
       <c r="E76">
-        <v>16.6144</v>
+        <v>16.86</v>
       </c>
       <c r="F76">
-        <v>18.1744</v>
+        <v>18.42</v>
       </c>
       <c r="G76">
         <v>10.9</v>
@@ -7519,37 +7519,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M76">
-        <v>2.66800192</v>
+        <v>2.704056</v>
       </c>
       <c r="N76">
-        <v>-0.3500427363265306</v>
+        <v>-0.3860968163265306</v>
       </c>
       <c r="O76">
-        <v>-0.05250641044897959</v>
+        <v>-0.05791452244897959</v>
       </c>
       <c r="P76">
-        <v>-0.297536325877551</v>
+        <v>-0.328182293877551</v>
       </c>
       <c r="Q76">
-        <v>0.7824636741224491</v>
+        <v>0.7518177061224491</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.345212619352099</v>
+        <v>0.357189124126183</v>
       </c>
       <c r="T76">
-        <v>3.586886028552126</v>
+        <v>3.730361469694211</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1303199502761304</v>
+        <v>0.1285823509391153</v>
       </c>
       <c r="W76">
-        <v>0.1276690312994641</v>
+        <v>0.1279241108821379</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8687996685075359</v>
+        <v>0.8572156729274354</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1852403641931492</v>
+        <v>0.1862503641931492</v>
       </c>
       <c r="C77">
-        <v>3.178980774654089</v>
+        <v>2.888882029860181</v>
       </c>
       <c r="D77">
-        <v>10.69898077465409</v>
+        <v>10.65448202986018</v>
       </c>
       <c r="E77">
-        <v>16.86</v>
+        <v>17.1056</v>
       </c>
       <c r="F77">
-        <v>18.42</v>
+        <v>18.6656</v>
       </c>
       <c r="G77">
         <v>10.9</v>
@@ -7601,37 +7601,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M77">
-        <v>2.704056</v>
+        <v>2.74011008</v>
       </c>
       <c r="N77">
-        <v>-0.3860968163265306</v>
+        <v>-0.4221508963265306</v>
       </c>
       <c r="O77">
-        <v>-0.05791452244897959</v>
+        <v>-0.06332263444897958</v>
       </c>
       <c r="P77">
-        <v>-0.328182293877551</v>
+        <v>-0.358828261877551</v>
       </c>
       <c r="Q77">
-        <v>0.7518177061224491</v>
+        <v>0.7211717381224491</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.357189124126183</v>
+        <v>0.370163670964774</v>
       </c>
       <c r="T77">
-        <v>3.730361469694211</v>
+        <v>3.885793197598137</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1285823509391153</v>
+        <v>0.1268904779004427</v>
       </c>
       <c r="W77">
-        <v>0.1279241108821379</v>
+        <v>0.128172477844215</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8572156729274354</v>
+        <v>0.845936519336285</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1862503641931492</v>
+        <v>0.1872603641931492</v>
       </c>
       <c r="C78">
-        <v>2.888882029860181</v>
+        <v>2.59915190647699</v>
       </c>
       <c r="D78">
-        <v>10.65448202986018</v>
+        <v>10.61035190647699</v>
       </c>
       <c r="E78">
-        <v>17.1056</v>
+        <v>17.3512</v>
       </c>
       <c r="F78">
-        <v>18.6656</v>
+        <v>18.9112</v>
       </c>
       <c r="G78">
         <v>10.9</v>
@@ -7683,37 +7683,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M78">
-        <v>2.74011008</v>
+        <v>2.77616416</v>
       </c>
       <c r="N78">
-        <v>-0.4221508963265306</v>
+        <v>-0.458204976326531</v>
       </c>
       <c r="O78">
-        <v>-0.06332263444897958</v>
+        <v>-0.06873074644897965</v>
       </c>
       <c r="P78">
-        <v>-0.358828261877551</v>
+        <v>-0.3894742298775514</v>
       </c>
       <c r="Q78">
-        <v>0.7211717381224491</v>
+        <v>0.6905257701224488</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.370163670964774</v>
+        <v>0.3842664392675902</v>
       </c>
       <c r="T78">
-        <v>3.885793197598137</v>
+        <v>4.054740727928491</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1268904779004427</v>
+        <v>0.1252425496160214</v>
       </c>
       <c r="W78">
-        <v>0.128172477844215</v>
+        <v>0.1284143937163681</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.845936519336285</v>
+        <v>0.834950330773476</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1872603641931492</v>
+        <v>0.1882703641931492</v>
       </c>
       <c r="C79">
-        <v>2.59915190647699</v>
+        <v>2.309785842985288</v>
       </c>
       <c r="D79">
-        <v>10.61035190647699</v>
+        <v>10.56658584298529</v>
       </c>
       <c r="E79">
-        <v>17.3512</v>
+        <v>17.5968</v>
       </c>
       <c r="F79">
-        <v>18.9112</v>
+        <v>19.1568</v>
       </c>
       <c r="G79">
         <v>10.9</v>
@@ -7765,37 +7765,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M79">
-        <v>2.77616416</v>
+        <v>2.81221824</v>
       </c>
       <c r="N79">
-        <v>-0.458204976326531</v>
+        <v>-0.494259056326531</v>
       </c>
       <c r="O79">
-        <v>-0.06873074644897965</v>
+        <v>-0.07413885844897965</v>
       </c>
       <c r="P79">
-        <v>-0.3894742298775514</v>
+        <v>-0.4201201978775513</v>
       </c>
       <c r="Q79">
-        <v>0.6905257701224488</v>
+        <v>0.6598798021224488</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3842664392675902</v>
+        <v>0.3996512774161172</v>
       </c>
       <c r="T79">
-        <v>4.054740727928491</v>
+        <v>4.239047124652513</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1252425496160214</v>
+        <v>0.1236368759029955</v>
       </c>
       <c r="W79">
-        <v>0.1284143937163681</v>
+        <v>0.1286501066174403</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.834950330773476</v>
+        <v>0.8242458393533032</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1882703641931492</v>
+        <v>0.1892803641931492</v>
       </c>
       <c r="C80">
-        <v>2.309785842985288</v>
+        <v>2.020779352818941</v>
       </c>
       <c r="D80">
-        <v>10.56658584298529</v>
+        <v>10.52317935281894</v>
       </c>
       <c r="E80">
-        <v>17.5968</v>
+        <v>17.8424</v>
       </c>
       <c r="F80">
-        <v>19.1568</v>
+        <v>19.4024</v>
       </c>
       <c r="G80">
         <v>10.9</v>
@@ -7847,37 +7847,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M80">
-        <v>2.81221824</v>
+        <v>2.84827232</v>
       </c>
       <c r="N80">
-        <v>-0.494259056326531</v>
+        <v>-0.530313136326531</v>
       </c>
       <c r="O80">
-        <v>-0.07413885844897965</v>
+        <v>-0.07954697044897964</v>
       </c>
       <c r="P80">
-        <v>-0.4201201978775513</v>
+        <v>-0.4507661658775514</v>
       </c>
       <c r="Q80">
-        <v>0.6598798021224488</v>
+        <v>0.6292338341224487</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3996512774161172</v>
+        <v>0.4165013382454561</v>
       </c>
       <c r="T80">
-        <v>4.239047124652513</v>
+        <v>4.440906511540729</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1236368759029955</v>
+        <v>0.1220718521573879</v>
       </c>
       <c r="W80">
-        <v>0.1286501066174403</v>
+        <v>0.1288798521032955</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8242458393533032</v>
+        <v>0.8138123477159196</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1892803641931492</v>
+        <v>0.1902903641931492</v>
       </c>
       <c r="C81">
-        <v>2.020779352818941</v>
+        <v>1.732128022831677</v>
       </c>
       <c r="D81">
-        <v>10.52317935281894</v>
+        <v>10.48012802283168</v>
       </c>
       <c r="E81">
-        <v>17.8424</v>
+        <v>18.088</v>
       </c>
       <c r="F81">
-        <v>19.4024</v>
+        <v>19.648</v>
       </c>
       <c r="G81">
         <v>10.9</v>
@@ -7929,37 +7929,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M81">
-        <v>2.84827232</v>
+        <v>2.8843264</v>
       </c>
       <c r="N81">
-        <v>-0.530313136326531</v>
+        <v>-0.566367216326531</v>
       </c>
       <c r="O81">
-        <v>-0.07954697044897964</v>
+        <v>-0.08495508244897965</v>
       </c>
       <c r="P81">
-        <v>-0.4507661658775514</v>
+        <v>-0.4814121338775513</v>
       </c>
       <c r="Q81">
-        <v>0.6292338341224487</v>
+        <v>0.5985878661224487</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4165013382454561</v>
+        <v>0.4350364051577288</v>
       </c>
       <c r="T81">
-        <v>4.440906511540729</v>
+        <v>4.662951837117765</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1220718521573879</v>
+        <v>0.1205459540054206</v>
       </c>
       <c r="W81">
-        <v>0.1288798521032955</v>
+        <v>0.1291038539520043</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8138123477159196</v>
+        <v>0.8036396933694706</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1902903641931492</v>
+        <v>0.2372747469581454</v>
       </c>
       <c r="C82">
-        <v>1.732128022831677</v>
+        <v>-0.1890962250388881</v>
       </c>
       <c r="D82">
-        <v>10.48012802283168</v>
+        <v>8.804503774961111</v>
       </c>
       <c r="E82">
-        <v>18.088</v>
+        <v>18.3336</v>
       </c>
       <c r="F82">
-        <v>19.648</v>
+        <v>19.8936</v>
       </c>
       <c r="G82">
         <v>10.9</v>
@@ -8011,45 +8011,45 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M82">
-        <v>2.8843264</v>
+        <v>3.99463488</v>
       </c>
       <c r="N82">
-        <v>-0.566367216326531</v>
+        <v>-1.676675696326531</v>
       </c>
       <c r="O82">
-        <v>-0.08495508244897965</v>
+        <v>-0.2515013544489796</v>
       </c>
       <c r="P82">
-        <v>-0.4814121338775513</v>
+        <v>-1.425174341877551</v>
       </c>
       <c r="Q82">
-        <v>0.5985878661224487</v>
+        <v>-0.3451743418775508</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4350364051577288</v>
+        <v>0.4672824410344317</v>
       </c>
       <c r="T82">
-        <v>4.662951837117765</v>
+        <v>5.049251037908365</v>
       </c>
       <c r="U82">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1205459540054206</v>
+        <v>0.08704021468691035</v>
       </c>
       <c r="W82">
-        <v>0.1291038539520043</v>
+        <v>0.1833223248908684</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.8036396933694706</v>
+        <v>0.5802680979127357</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2372747469581454</v>
+        <v>0.2388247469581454</v>
       </c>
       <c r="C83">
-        <v>-0.1890962250388881</v>
+        <v>-0.4808926536540383</v>
       </c>
       <c r="D83">
-        <v>8.804503774961111</v>
+        <v>8.75830734634596</v>
       </c>
       <c r="E83">
-        <v>18.3336</v>
+        <v>18.5792</v>
       </c>
       <c r="F83">
-        <v>19.8936</v>
+        <v>20.1392</v>
       </c>
       <c r="G83">
         <v>10.9</v>
@@ -8093,37 +8093,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M83">
-        <v>3.99463488</v>
+        <v>4.04395136</v>
       </c>
       <c r="N83">
-        <v>-1.676675696326531</v>
+        <v>-1.725992176326531</v>
       </c>
       <c r="O83">
-        <v>-0.2515013544489796</v>
+        <v>-0.2588988264489796</v>
       </c>
       <c r="P83">
-        <v>-1.425174341877551</v>
+        <v>-1.467093349877551</v>
       </c>
       <c r="Q83">
-        <v>-0.3451743418775508</v>
+        <v>-0.3870933498775513</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4672824410344317</v>
+        <v>0.4906981322030112</v>
       </c>
       <c r="T83">
-        <v>5.049251037908365</v>
+        <v>5.329764984458829</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.08704021468691035</v>
+        <v>0.08597874865414315</v>
       </c>
       <c r="W83">
-        <v>0.1833223248908684</v>
+        <v>0.1835354672702481</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5802680979127357</v>
+        <v>0.5731916576942877</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2388247469581454</v>
+        <v>0.2403747469581454</v>
       </c>
       <c r="C84">
-        <v>-0.4808926536540383</v>
+        <v>-0.7722068356745275</v>
       </c>
       <c r="D84">
-        <v>8.75830734634596</v>
+        <v>8.712593164325472</v>
       </c>
       <c r="E84">
-        <v>18.5792</v>
+        <v>18.8248</v>
       </c>
       <c r="F84">
-        <v>20.1392</v>
+        <v>20.3848</v>
       </c>
       <c r="G84">
         <v>10.9</v>
@@ -8175,37 +8175,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M84">
-        <v>4.04395136</v>
+        <v>4.09326784</v>
       </c>
       <c r="N84">
-        <v>-1.725992176326531</v>
+        <v>-1.775308656326531</v>
       </c>
       <c r="O84">
-        <v>-0.2588988264489796</v>
+        <v>-0.2662962984489796</v>
       </c>
       <c r="P84">
-        <v>-1.467093349877551</v>
+        <v>-1.509012357877551</v>
       </c>
       <c r="Q84">
-        <v>-0.3870933498775513</v>
+        <v>-0.4290123578775511</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4906981322030112</v>
+        <v>0.5168686105678942</v>
       </c>
       <c r="T84">
-        <v>5.329764984458829</v>
+        <v>5.643280571779938</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.08597874865414315</v>
+        <v>0.08494286011614142</v>
       </c>
       <c r="W84">
-        <v>0.1835354672702481</v>
+        <v>0.1837434736886788</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5731916576942877</v>
+        <v>0.5662857341076095</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2403747469581454</v>
+        <v>0.2419247469581454</v>
       </c>
       <c r="C85">
-        <v>-0.7722068356745275</v>
+        <v>-1.063046283181684</v>
       </c>
       <c r="D85">
-        <v>8.712593164325472</v>
+        <v>8.667353716818317</v>
       </c>
       <c r="E85">
-        <v>18.8248</v>
+        <v>19.0704</v>
       </c>
       <c r="F85">
-        <v>20.3848</v>
+        <v>20.6304</v>
       </c>
       <c r="G85">
         <v>10.9</v>
@@ -8257,37 +8257,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M85">
-        <v>4.09326784</v>
+        <v>4.14258432</v>
       </c>
       <c r="N85">
-        <v>-1.775308656326531</v>
+        <v>-1.824625136326531</v>
       </c>
       <c r="O85">
-        <v>-0.2662962984489796</v>
+        <v>-0.2736937704489796</v>
       </c>
       <c r="P85">
-        <v>-1.509012357877551</v>
+        <v>-1.550931365877551</v>
       </c>
       <c r="Q85">
-        <v>-0.4290123578775511</v>
+        <v>-0.4709313658775511</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5168686105678942</v>
+        <v>0.5463103987283877</v>
       </c>
       <c r="T85">
-        <v>5.643280571779938</v>
+        <v>5.995985607516185</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.08494286011614142</v>
+        <v>0.08393163559094928</v>
       </c>
       <c r="W85">
-        <v>0.1837434736886788</v>
+        <v>0.1839465275733374</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5662857341076095</v>
+        <v>0.5595442372729952</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2419247469581454</v>
+        <v>0.2434747469581454</v>
       </c>
       <c r="C86">
-        <v>-1.063046283181681</v>
+        <v>-1.35341835303926</v>
       </c>
       <c r="D86">
-        <v>8.667353716818317</v>
+        <v>8.622581646960736</v>
       </c>
       <c r="E86">
-        <v>19.0704</v>
+        <v>19.316</v>
       </c>
       <c r="F86">
-        <v>20.6304</v>
+        <v>20.876</v>
       </c>
       <c r="G86">
         <v>10.9</v>
@@ -8339,37 +8339,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M86">
-        <v>4.14258432</v>
+        <v>4.1919008</v>
       </c>
       <c r="N86">
-        <v>-1.824625136326531</v>
+        <v>-1.873941616326531</v>
       </c>
       <c r="O86">
-        <v>-0.2736937704489796</v>
+        <v>-0.2810912424489796</v>
       </c>
       <c r="P86">
-        <v>-1.550931365877551</v>
+        <v>-1.592850373877551</v>
       </c>
       <c r="Q86">
-        <v>-0.4709313658775511</v>
+        <v>-0.5128503738775509</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5463103987283874</v>
+        <v>0.5796777586436132</v>
       </c>
       <c r="T86">
-        <v>5.995985607516181</v>
+        <v>6.395717981350592</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.08393163559094928</v>
+        <v>0.08294420458399693</v>
       </c>
       <c r="W86">
-        <v>0.1839465275733374</v>
+        <v>0.1841448037195334</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5595442372729952</v>
+        <v>0.5529613638933129</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2434747469581454</v>
+        <v>0.2450247469581454</v>
       </c>
       <c r="C87">
-        <v>-1.35341835303926</v>
+        <v>-1.643330250881789</v>
       </c>
       <c r="D87">
-        <v>8.622581646960736</v>
+        <v>8.578269749118208</v>
       </c>
       <c r="E87">
-        <v>19.316</v>
+        <v>19.5616</v>
       </c>
       <c r="F87">
-        <v>20.876</v>
+        <v>21.1216</v>
       </c>
       <c r="G87">
         <v>10.9</v>
@@ -8421,37 +8421,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M87">
-        <v>4.1919008</v>
+        <v>4.24121728</v>
       </c>
       <c r="N87">
-        <v>-1.873941616326531</v>
+        <v>-1.92325809632653</v>
       </c>
       <c r="O87">
-        <v>-0.2810912424489796</v>
+        <v>-0.2884887144489796</v>
       </c>
       <c r="P87">
-        <v>-1.592850373877551</v>
+        <v>-1.634769381877551</v>
       </c>
       <c r="Q87">
-        <v>-0.5128503738775509</v>
+        <v>-0.5547693818775508</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5796777586436132</v>
+        <v>0.6178118842610142</v>
       </c>
       <c r="T87">
-        <v>6.395717981350592</v>
+        <v>6.852554980018493</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.08294420458399693</v>
+        <v>0.08197973708883417</v>
       </c>
       <c r="W87">
-        <v>0.1841448037195334</v>
+        <v>0.1843384687925621</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5529613638933129</v>
+        <v>0.546531580592228</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2450247469581454</v>
+        <v>0.2465747469581454</v>
       </c>
       <c r="C88">
-        <v>-1.643330250881789</v>
+        <v>-1.932789034980562</v>
       </c>
       <c r="D88">
-        <v>8.578269749118208</v>
+        <v>8.534410965019438</v>
       </c>
       <c r="E88">
-        <v>19.5616</v>
+        <v>19.8072</v>
       </c>
       <c r="F88">
-        <v>21.1216</v>
+        <v>21.3672</v>
       </c>
       <c r="G88">
         <v>10.9</v>
@@ -8503,37 +8503,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M88">
-        <v>4.24121728</v>
+        <v>4.290533760000001</v>
       </c>
       <c r="N88">
-        <v>-1.92325809632653</v>
+        <v>-1.972574576326531</v>
       </c>
       <c r="O88">
-        <v>-0.2884887144489796</v>
+        <v>-0.2958861864489797</v>
       </c>
       <c r="P88">
-        <v>-1.634769381877551</v>
+        <v>-1.676688389877552</v>
       </c>
       <c r="Q88">
-        <v>-0.5547693818775508</v>
+        <v>-0.5966883898775515</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6178118842610142</v>
+        <v>0.6618127984349383</v>
       </c>
       <c r="T88">
-        <v>6.852554980018493</v>
+        <v>7.379674593866069</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.08197973708883417</v>
+        <v>0.08103744126022687</v>
       </c>
       <c r="W88">
-        <v>0.1843384687925621</v>
+        <v>0.1845276817949465</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.546531580592228</v>
+        <v>0.5402496084015125</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2465747469581454</v>
+        <v>0.2481247469581454</v>
       </c>
       <c r="C89">
-        <v>-1.932789034980562</v>
+        <v>-2.221801619991666</v>
       </c>
       <c r="D89">
-        <v>8.534410965019438</v>
+        <v>8.490998380008332</v>
       </c>
       <c r="E89">
-        <v>19.8072</v>
+        <v>20.0528</v>
       </c>
       <c r="F89">
-        <v>21.3672</v>
+        <v>21.6128</v>
       </c>
       <c r="G89">
         <v>10.9</v>
@@ -8585,37 +8585,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M89">
-        <v>4.290533760000001</v>
+        <v>4.339850240000001</v>
       </c>
       <c r="N89">
-        <v>-1.972574576326531</v>
+        <v>-2.021891056326531</v>
       </c>
       <c r="O89">
-        <v>-0.2958861864489797</v>
+        <v>-0.3032836584489796</v>
       </c>
       <c r="P89">
-        <v>-1.676688389877552</v>
+        <v>-1.718607397877551</v>
       </c>
       <c r="Q89">
-        <v>-0.5966883898775515</v>
+        <v>-0.6386073978775513</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6618127984349383</v>
+        <v>0.7131471983045167</v>
       </c>
       <c r="T89">
-        <v>7.379674593866069</v>
+        <v>7.994647476688242</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.08103744126022687</v>
+        <v>0.08011656124590612</v>
       </c>
       <c r="W89">
-        <v>0.1845276817949465</v>
+        <v>0.184712594501822</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5402496084015125</v>
+        <v>0.5341104083060408</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2481247469581454</v>
+        <v>0.2496747469581454</v>
       </c>
       <c r="C90">
-        <v>-2.221801619991666</v>
+        <v>-2.510374780590194</v>
       </c>
       <c r="D90">
-        <v>8.490998380008332</v>
+        <v>8.448025219409805</v>
       </c>
       <c r="E90">
-        <v>20.0528</v>
+        <v>20.2984</v>
       </c>
       <c r="F90">
-        <v>21.6128</v>
+        <v>21.8584</v>
       </c>
       <c r="G90">
         <v>10.9</v>
@@ -8667,37 +8667,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M90">
-        <v>4.339850240000001</v>
+        <v>4.38916672</v>
       </c>
       <c r="N90">
-        <v>-2.021891056326531</v>
+        <v>-2.071207536326531</v>
       </c>
       <c r="O90">
-        <v>-0.3032836584489796</v>
+        <v>-0.3106811304489797</v>
       </c>
       <c r="P90">
-        <v>-1.718607397877551</v>
+        <v>-1.760526405877551</v>
       </c>
       <c r="Q90">
-        <v>-0.6386073978775513</v>
+        <v>-0.6805264058775513</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7131471983045167</v>
+        <v>0.7738151254231089</v>
       </c>
       <c r="T90">
-        <v>7.994647476688242</v>
+        <v>8.721433610932626</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.08011656124590612</v>
+        <v>0.07921637516449144</v>
       </c>
       <c r="W90">
-        <v>0.184712594501822</v>
+        <v>0.1848933518669701</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5341104083060408</v>
+        <v>0.5281091677632763</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2496747469581454</v>
+        <v>0.2512247469581454</v>
       </c>
       <c r="C91">
-        <v>-2.510374780590194</v>
+        <v>-2.798515154994618</v>
       </c>
       <c r="D91">
-        <v>8.448025219409805</v>
+        <v>8.405484845005383</v>
       </c>
       <c r="E91">
-        <v>20.2984</v>
+        <v>20.544</v>
       </c>
       <c r="F91">
-        <v>21.8584</v>
+        <v>22.104</v>
       </c>
       <c r="G91">
         <v>10.9</v>
@@ -8749,37 +8749,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M91">
-        <v>4.38916672</v>
+        <v>4.4384832</v>
       </c>
       <c r="N91">
-        <v>-2.071207536326531</v>
+        <v>-2.120524016326531</v>
       </c>
       <c r="O91">
-        <v>-0.3106811304489797</v>
+        <v>-0.3180786024489796</v>
       </c>
       <c r="P91">
-        <v>-1.760526405877551</v>
+        <v>-1.802445413877551</v>
       </c>
       <c r="Q91">
-        <v>-0.6805264058775513</v>
+        <v>-0.7224454138775511</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7738151254231089</v>
+        <v>0.84661663796542</v>
       </c>
       <c r="T91">
-        <v>8.721433610932626</v>
+        <v>9.593576972025891</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.07921637516449144</v>
+        <v>0.07833619321821932</v>
       </c>
       <c r="W91">
-        <v>0.1848933518669701</v>
+        <v>0.1850700924017816</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5281091677632763</v>
+        <v>0.5222412881214622</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2512247469581454</v>
+        <v>0.2527747469581454</v>
       </c>
       <c r="C92">
-        <v>-2.798515154994618</v>
+        <v>-3.086229248385255</v>
       </c>
       <c r="D92">
-        <v>8.405484845005383</v>
+        <v>8.363370751614745</v>
       </c>
       <c r="E92">
-        <v>20.544</v>
+        <v>20.7896</v>
       </c>
       <c r="F92">
-        <v>22.104</v>
+        <v>22.3496</v>
       </c>
       <c r="G92">
         <v>10.9</v>
@@ -8831,37 +8831,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M92">
-        <v>4.4384832</v>
+        <v>4.48779968</v>
       </c>
       <c r="N92">
-        <v>-2.120524016326531</v>
+        <v>-2.169840496326531</v>
       </c>
       <c r="O92">
-        <v>-0.3180786024489796</v>
+        <v>-0.3254760744489796</v>
       </c>
       <c r="P92">
-        <v>-1.802445413877551</v>
+        <v>-1.844364421877551</v>
       </c>
       <c r="Q92">
-        <v>-0.7224454138775511</v>
+        <v>-0.7643644218775512</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.84661663796542</v>
+        <v>0.9355962644060223</v>
       </c>
       <c r="T92">
-        <v>9.593576972025891</v>
+        <v>10.65952996891766</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.07833619321821932</v>
+        <v>0.07747535593010701</v>
       </c>
       <c r="W92">
-        <v>0.1850700924017816</v>
+        <v>0.1852429485292345</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5222412881214622</v>
+        <v>0.5165023728673801</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2527747469581454</v>
+        <v>0.2543247469581454</v>
       </c>
       <c r="C93">
-        <v>-3.086229248385255</v>
+        <v>-3.373523436220466</v>
       </c>
       <c r="D93">
-        <v>8.363370751614745</v>
+        <v>8.321676563779532</v>
       </c>
       <c r="E93">
-        <v>20.7896</v>
+        <v>21.0352</v>
       </c>
       <c r="F93">
-        <v>22.3496</v>
+        <v>22.5952</v>
       </c>
       <c r="G93">
         <v>10.9</v>
@@ -8913,37 +8913,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M93">
-        <v>4.48779968</v>
+        <v>4.53711616</v>
       </c>
       <c r="N93">
-        <v>-2.169840496326531</v>
+        <v>-2.219156976326531</v>
       </c>
       <c r="O93">
-        <v>-0.3254760744489796</v>
+        <v>-0.3328735464489796</v>
       </c>
       <c r="P93">
-        <v>-1.844364421877551</v>
+        <v>-1.886283429877551</v>
       </c>
       <c r="Q93">
-        <v>-0.7643644218775512</v>
+        <v>-0.806283429877551</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9355962644060223</v>
+        <v>1.046820797456776</v>
       </c>
       <c r="T93">
-        <v>10.65952996891766</v>
+        <v>11.99197121503237</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.07747535593010701</v>
+        <v>0.07663323249608413</v>
       </c>
       <c r="W93">
-        <v>0.1852429485292345</v>
+        <v>0.1854120469147863</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5165023728673801</v>
+        <v>0.5108882166405608</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2543247469581454</v>
+        <v>0.2558747469581454</v>
       </c>
       <c r="C94">
-        <v>-3.373523436220466</v>
+        <v>-3.660403967454151</v>
       </c>
       <c r="D94">
-        <v>8.321676563779532</v>
+        <v>8.280396032545848</v>
       </c>
       <c r="E94">
-        <v>21.0352</v>
+        <v>21.2808</v>
       </c>
       <c r="F94">
-        <v>22.5952</v>
+        <v>22.8408</v>
       </c>
       <c r="G94">
         <v>10.9</v>
@@ -8995,37 +8995,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M94">
-        <v>4.53711616</v>
+        <v>4.586432640000001</v>
       </c>
       <c r="N94">
-        <v>-2.219156976326531</v>
+        <v>-2.268473456326531</v>
       </c>
       <c r="O94">
-        <v>-0.3328735464489796</v>
+        <v>-0.3402710184489797</v>
       </c>
       <c r="P94">
-        <v>-1.886283429877551</v>
+        <v>-1.928202437877552</v>
       </c>
       <c r="Q94">
-        <v>-0.806283429877551</v>
+        <v>-0.8482024378775517</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.046820797456776</v>
+        <v>1.189823768522029</v>
       </c>
       <c r="T94">
-        <v>11.99197121503237</v>
+        <v>13.70510996003699</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.07663323249608413</v>
+        <v>0.07580921924343804</v>
       </c>
       <c r="W94">
-        <v>0.1854120469147863</v>
+        <v>0.1855775087759176</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5108882166405608</v>
+        <v>0.5053947949562536</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2558747469581454</v>
+        <v>0.2574247469581454</v>
       </c>
       <c r="C95">
-        <v>-3.660403967454151</v>
+        <v>-3.946876967657946</v>
       </c>
       <c r="D95">
-        <v>8.280396032545848</v>
+        <v>8.239523032342055</v>
       </c>
       <c r="E95">
-        <v>21.2808</v>
+        <v>21.5264</v>
       </c>
       <c r="F95">
-        <v>22.8408</v>
+        <v>23.0864</v>
       </c>
       <c r="G95">
         <v>10.9</v>
@@ -9077,37 +9077,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M95">
-        <v>4.586432640000001</v>
+        <v>4.635749120000001</v>
       </c>
       <c r="N95">
-        <v>-2.268473456326531</v>
+        <v>-2.317789936326531</v>
       </c>
       <c r="O95">
-        <v>-0.3402710184489797</v>
+        <v>-0.3476684904489797</v>
       </c>
       <c r="P95">
-        <v>-1.928202437877552</v>
+        <v>-1.970121445877552</v>
       </c>
       <c r="Q95">
-        <v>-0.8482024378775517</v>
+        <v>-0.8901214458775515</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.189823768522029</v>
+        <v>1.380494396609034</v>
       </c>
       <c r="T95">
-        <v>13.70510996003699</v>
+        <v>15.9892949533765</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.07580921924343804</v>
+        <v>0.07500273818765679</v>
       </c>
       <c r="W95">
-        <v>0.1855775087759176</v>
+        <v>0.1857394501719185</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5053947949562536</v>
+        <v>0.5000182545843785</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2574247469581454</v>
+        <v>0.2931263473921723</v>
       </c>
       <c r="C96">
-        <v>-3.946876967657946</v>
+        <v>-5.033634222433651</v>
       </c>
       <c r="D96">
-        <v>8.239523032342055</v>
+        <v>7.39836577756635</v>
       </c>
       <c r="E96">
-        <v>21.5264</v>
+        <v>21.772</v>
       </c>
       <c r="F96">
-        <v>23.0864</v>
+        <v>23.332</v>
       </c>
       <c r="G96">
         <v>10.9</v>
@@ -9159,45 +9159,45 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M96">
-        <v>4.635749120000001</v>
+        <v>5.5016856</v>
       </c>
       <c r="N96">
-        <v>-2.317789936326531</v>
+        <v>-3.183726416326531</v>
       </c>
       <c r="O96">
-        <v>-0.3476684904489797</v>
+        <v>-0.4775589624489796</v>
       </c>
       <c r="P96">
-        <v>-1.970121445877552</v>
+        <v>-2.706167453877551</v>
       </c>
       <c r="Q96">
-        <v>-0.8901214458775515</v>
+        <v>-1.626167453877551</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.380494396609034</v>
+        <v>1.665465284611379</v>
       </c>
       <c r="T96">
-        <v>15.9892949533765</v>
+        <v>19.40317276163841</v>
       </c>
       <c r="U96">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07500273818765679</v>
+        <v>0.06319770027407971</v>
       </c>
       <c r="W96">
-        <v>0.1857394501719185</v>
+        <v>0.220897982275372</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.5000182545843785</v>
+        <v>0.4213180018271981</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2931263473921723</v>
+        <v>0.2950263473921723</v>
       </c>
       <c r="C97">
-        <v>-5.033634222433651</v>
+        <v>-5.319212464680991</v>
       </c>
       <c r="D97">
-        <v>7.39836577756635</v>
+        <v>7.35838753531901</v>
       </c>
       <c r="E97">
-        <v>21.772</v>
+        <v>22.0176</v>
       </c>
       <c r="F97">
-        <v>23.332</v>
+        <v>23.5776</v>
       </c>
       <c r="G97">
         <v>10.9</v>
@@ -9241,37 +9241,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M97">
-        <v>5.5016856</v>
+        <v>5.559598080000001</v>
       </c>
       <c r="N97">
-        <v>-3.183726416326531</v>
+        <v>-3.241638896326531</v>
       </c>
       <c r="O97">
-        <v>-0.4775589624489796</v>
+        <v>-0.4862458344489797</v>
       </c>
       <c r="P97">
-        <v>-2.706167453877551</v>
+        <v>-2.755393061877552</v>
       </c>
       <c r="Q97">
-        <v>-1.626167453877551</v>
+        <v>-1.675393061877552</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.665465284611379</v>
+        <v>2.070381605764225</v>
       </c>
       <c r="T97">
-        <v>19.40317276163841</v>
+        <v>24.25396595204803</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06319770027407971</v>
+        <v>0.06253939089622471</v>
       </c>
       <c r="W97">
-        <v>0.220897982275372</v>
+        <v>0.2210532116266702</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4213180018271981</v>
+        <v>0.416929272641498</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2950263473921723</v>
+        <v>0.2969263473921723</v>
       </c>
       <c r="C98">
-        <v>-5.319212464680987</v>
+        <v>-5.604360971533207</v>
       </c>
       <c r="D98">
-        <v>7.35838753531901</v>
+        <v>7.318839028466788</v>
       </c>
       <c r="E98">
-        <v>22.0176</v>
+        <v>22.2632</v>
       </c>
       <c r="F98">
-        <v>23.5776</v>
+        <v>23.8232</v>
       </c>
       <c r="G98">
         <v>10.9</v>
@@ -9323,37 +9323,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M98">
-        <v>5.55959808</v>
+        <v>5.617510559999999</v>
       </c>
       <c r="N98">
-        <v>-3.24163889632653</v>
+        <v>-3.29955137632653</v>
       </c>
       <c r="O98">
-        <v>-0.4862458344489795</v>
+        <v>-0.4949327064489795</v>
       </c>
       <c r="P98">
-        <v>-2.755393061877551</v>
+        <v>-2.80461866987755</v>
       </c>
       <c r="Q98">
-        <v>-1.675393061877551</v>
+        <v>-1.72461866987755</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.070381605764219</v>
+        <v>2.745242141018959</v>
       </c>
       <c r="T98">
-        <v>24.25396595204796</v>
+        <v>32.33862126939729</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06253939089622472</v>
+        <v>0.06189465490760385</v>
       </c>
       <c r="W98">
-        <v>0.2210532116266702</v>
+        <v>0.221205240372787</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4169292726414981</v>
+        <v>0.412631032717359</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2969263473921723</v>
+        <v>0.2988263473921723</v>
       </c>
       <c r="C99">
-        <v>-5.604360971533207</v>
+        <v>-5.889086634936849</v>
       </c>
       <c r="D99">
-        <v>7.318839028466788</v>
+        <v>7.27971336506315</v>
       </c>
       <c r="E99">
-        <v>22.2632</v>
+        <v>22.5088</v>
       </c>
       <c r="F99">
-        <v>23.8232</v>
+        <v>24.0688</v>
       </c>
       <c r="G99">
         <v>10.9</v>
@@ -9405,37 +9405,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M99">
-        <v>5.617510559999999</v>
+        <v>5.67542304</v>
       </c>
       <c r="N99">
-        <v>-3.29955137632653</v>
+        <v>-3.357463856326531</v>
       </c>
       <c r="O99">
-        <v>-0.4949327064489795</v>
+        <v>-0.5036195784489795</v>
       </c>
       <c r="P99">
-        <v>-2.80461866987755</v>
+        <v>-2.853844277877551</v>
       </c>
       <c r="Q99">
-        <v>-1.72461866987755</v>
+        <v>-1.773844277877551</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.745242141018959</v>
+        <v>4.094963211528439</v>
       </c>
       <c r="T99">
-        <v>32.33862126939729</v>
+        <v>48.50793190409593</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06189465490760385</v>
+        <v>0.06126307679630176</v>
       </c>
       <c r="W99">
-        <v>0.221205240372787</v>
+        <v>0.2213541664914321</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.412631032717359</v>
+        <v>0.4084205119753451</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2988263473921723</v>
+        <v>0.3007263473921722</v>
       </c>
       <c r="C100">
-        <v>-5.889086634936849</v>
+        <v>-6.173396200247907</v>
       </c>
       <c r="D100">
-        <v>7.27971336506315</v>
+        <v>7.241003799752093</v>
       </c>
       <c r="E100">
-        <v>22.5088</v>
+        <v>22.7544</v>
       </c>
       <c r="F100">
-        <v>24.0688</v>
+        <v>24.3144</v>
       </c>
       <c r="G100">
         <v>10.9</v>
@@ -9487,37 +9487,37 @@
         <v>2.317959183673469</v>
       </c>
       <c r="M100">
-        <v>5.67542304</v>
+        <v>5.73333552</v>
       </c>
       <c r="N100">
-        <v>-3.357463856326531</v>
+        <v>-3.41537633632653</v>
       </c>
       <c r="O100">
-        <v>-0.5036195784489795</v>
+        <v>-0.5123064504489795</v>
       </c>
       <c r="P100">
-        <v>-2.853844277877551</v>
+        <v>-2.903069885877551</v>
       </c>
       <c r="Q100">
-        <v>-1.773844277877551</v>
+        <v>-1.823069885877551</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.094963211528439</v>
+        <v>8.144126423056877</v>
       </c>
       <c r="T100">
-        <v>48.50793190409593</v>
+        <v>97.01586380819184</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06126307679630176</v>
+        <v>0.06064425783876336</v>
       </c>
       <c r="W100">
-        <v>0.2213541664914321</v>
+        <v>0.2215000840016196</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4084205119753451</v>
+        <v>0.4042950522584224</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3007263473921722</v>
-      </c>
-      <c r="C101">
-        <v>-6.173396200247907</v>
-      </c>
-      <c r="D101">
-        <v>7.241003799752093</v>
-      </c>
-      <c r="E101">
-        <v>22.7544</v>
-      </c>
-      <c r="F101">
-        <v>24.3144</v>
-      </c>
-      <c r="G101">
-        <v>10.9</v>
-      </c>
-      <c r="H101">
-        <v>23</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.397959183673469</v>
-      </c>
-      <c r="K101">
-        <v>1.08</v>
-      </c>
-      <c r="L101">
-        <v>2.317959183673469</v>
-      </c>
-      <c r="M101">
-        <v>5.73333552</v>
-      </c>
-      <c r="N101">
-        <v>-3.41537633632653</v>
-      </c>
-      <c r="O101">
-        <v>-0.5123064504489795</v>
-      </c>
-      <c r="P101">
-        <v>-2.903069885877551</v>
-      </c>
-      <c r="Q101">
-        <v>-1.823069885877551</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.144126423056877</v>
-      </c>
-      <c r="T101">
-        <v>97.01586380819184</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06064425783876336</v>
-      </c>
-      <c r="W101">
-        <v>0.2215000840016196</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4042950522584224</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
